--- a/marks.xlsx
+++ b/marks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tmp\FAKT_INFORMATICS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBCBBA0-70A1-4BA7-99CB-6233D3302496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F2D846-8A01-40CB-BFD5-D682F57526E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{9546C0DC-CDD5-4F7B-8A2F-88672275CD35}"/>
   </bookViews>
@@ -1818,7 +1818,9 @@
       <c r="A10" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="12"/>
+      <c r="B10" s="12">
+        <v>1</v>
+      </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
@@ -1828,7 +1830,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1941,7 +1943,9 @@
       <c r="A17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="13"/>
+      <c r="B17" s="13">
+        <v>2</v>
+      </c>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -1951,7 +1955,7 @@
       <c r="I17" s="13"/>
       <c r="J17" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1975,7 +1979,9 @@
       <c r="A19" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="13"/>
+      <c r="B19" s="13">
+        <v>2</v>
+      </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -1985,7 +1991,7 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tmp\FAKT_INFORMATICS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Vanya\inf\FAKT_INFORMATICS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F2D846-8A01-40CB-BFD5-D682F57526E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA38F044-EB03-4404-B27D-7481AF7E621D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{9546C0DC-CDD5-4F7B-8A2F-88672275CD35}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{9546C0DC-CDD5-4F7B-8A2F-88672275CD35}"/>
   </bookViews>
   <sheets>
     <sheet name="посещения" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="57">
   <si>
     <t>Column1</t>
   </si>
@@ -162,15 +162,9 @@
     <t>Коломоец</t>
   </si>
   <si>
-    <t xml:space="preserve">Коломоец </t>
-  </si>
-  <si>
     <t>Кукушкин</t>
   </si>
   <si>
-    <t>Максим</t>
-  </si>
-  <si>
     <t>Моисеев</t>
   </si>
   <si>
@@ -181,9 +175,6 @@
   </si>
   <si>
     <t>Подкорытов</t>
-  </si>
-  <si>
-    <t>Сахно</t>
   </si>
   <si>
     <t>Титова</t>
@@ -232,7 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +240,13 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -352,10 +350,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -370,9 +369,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{87215833-4AB8-4C7B-B4E3-32D122E4BDEB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -388,9 +389,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -428,7 +429,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -534,7 +535,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -676,7 +677,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -684,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A2530F-15E7-4948-899C-7807B8BB0FF9}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -947,8 +948,8 @@
       <c r="C6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>32</v>
+      <c r="D6" s="5">
+        <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>33</v>
@@ -988,52 +989,52 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" s="9" t="s">
+      <c r="B7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="6" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1092,25 +1093,25 @@
         <v>40</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>32</v>
@@ -1142,22 +1143,22 @@
         <v>41</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>32</v>
@@ -1192,25 +1193,25 @@
         <v>42</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>32</v>
@@ -1238,402 +1239,252 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="5">
+      <c r="B12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="5">
         <v>1</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P13" s="9" t="s">
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P14" s="6" t="s">
+      <c r="B14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" s="9" t="s">
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="5">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5">
-        <v>1</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" s="9" t="s">
+      <c r="B16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1644,7 +1495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C65BD6-32E4-4AC1-8AA8-7D04B17B4286}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:BE37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -1666,31 +1517,31 @@
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="J2" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1704,12 +1555,14 @@
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="G3" s="13">
+        <v>6</v>
+      </c>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
       <c r="J3" s="13">
         <f>MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1721,12 +1574,14 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="12">
+        <v>8</v>
+      </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="13">
         <f t="shared" ref="J4:J19" si="0">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1738,12 +1593,14 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="G5" s="13">
+        <v>9</v>
+      </c>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1755,72 +1612,82 @@
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="12">
+        <v>6</v>
+      </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12">
+        <v>5</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
       <c r="J7" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="12"/>
+      <c r="B8" s="12">
+        <v>1</v>
+      </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="G8" s="12">
+        <v>9</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="13">
+        <v>2</v>
+      </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="G9" s="13">
+        <v>6</v>
+      </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="12">
-        <v>1</v>
-      </c>
+      <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
@@ -1829,17 +1696,15 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="13">
-        <v>2</v>
-      </c>
+      <c r="B11" s="13"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -1848,157 +1713,852 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>MIN(10, ROUNDUP((B11+C11+D11+E11+F11)/3+G11/3+H11/3+I11,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="B12" s="13">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13">
+        <v>7</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
       <c r="J12" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12">
+        <v>6</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(10, ROUNDUP((B13+C13+D13+E13+F13)/3+G13/3+H13/3+I13,0))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
+      <c r="B14" s="13">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13">
+        <v>8</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
       <c r="J14" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12">
+        <v>9</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13">
+        <f>MIN(10, ROUNDUP((B15+C15+D15+E15+F15)/3+G15/3+H15/3+I15,0))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="13">
         <v>2</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13">
+        <v>6</v>
+      </c>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
       <c r="J16" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="13">
-        <v>2</v>
-      </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="13">
-        <v>2</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K19" s="8"/>
+        <f>MIN(10, ROUNDUP((B16+C16+D16+E16+F16)/3+G16/3+H16/3+I16,0))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="K17" s="8"/>
+    </row>
+    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
+    </row>
+    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+      <c r="AE26" s="14"/>
+      <c r="AF26" s="14"/>
+      <c r="AG26" s="14"/>
+      <c r="AH26" s="14"/>
+      <c r="AI26" s="14"/>
+      <c r="AJ26" s="14"/>
+      <c r="AK26" s="14"/>
+      <c r="AL26" s="14"/>
+      <c r="AM26" s="14"/>
+      <c r="AN26" s="14"/>
+      <c r="AO26" s="14"/>
+      <c r="AP26" s="14"/>
+      <c r="AQ26" s="14"/>
+      <c r="AR26" s="14"/>
+      <c r="AS26" s="14"/>
+      <c r="AT26" s="14"/>
+      <c r="AU26" s="14"/>
+      <c r="AV26" s="14"/>
+      <c r="AW26" s="14"/>
+      <c r="AX26" s="14"/>
+      <c r="AY26" s="14"/>
+      <c r="AZ26" s="14"/>
+      <c r="BA26" s="14"/>
+      <c r="BB26" s="14"/>
+      <c r="BC26" s="14"/>
+      <c r="BD26" s="14">
+        <v>18</v>
+      </c>
+      <c r="BE26" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
+      <c r="AE27" s="14"/>
+      <c r="AF27" s="14"/>
+      <c r="AG27" s="14"/>
+      <c r="AH27" s="14"/>
+      <c r="AI27" s="14"/>
+      <c r="AJ27" s="14"/>
+      <c r="AK27" s="14"/>
+      <c r="AL27" s="14"/>
+      <c r="AM27" s="14"/>
+      <c r="AN27" s="14"/>
+      <c r="AO27" s="14"/>
+      <c r="AP27" s="14"/>
+      <c r="AQ27" s="14"/>
+      <c r="AR27" s="14"/>
+      <c r="AS27" s="14"/>
+      <c r="AT27" s="14"/>
+      <c r="AU27" s="14"/>
+      <c r="AV27" s="14"/>
+      <c r="AW27" s="14"/>
+      <c r="AX27" s="14"/>
+      <c r="AY27" s="14"/>
+      <c r="AZ27" s="14"/>
+      <c r="BA27" s="14"/>
+      <c r="BB27" s="14"/>
+      <c r="BC27" s="14"/>
+      <c r="BD27" s="14">
+        <v>11</v>
+      </c>
+      <c r="BE27" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
+      <c r="AE28" s="14"/>
+      <c r="AF28" s="14"/>
+      <c r="AG28" s="14"/>
+      <c r="AH28" s="14"/>
+      <c r="AI28" s="14"/>
+      <c r="AJ28" s="14"/>
+      <c r="AK28" s="14"/>
+      <c r="AL28" s="14"/>
+      <c r="AM28" s="14"/>
+      <c r="AN28" s="14"/>
+      <c r="AO28" s="14"/>
+      <c r="AP28" s="14"/>
+      <c r="AQ28" s="14"/>
+      <c r="AR28" s="14"/>
+      <c r="AS28" s="14"/>
+      <c r="AT28" s="14"/>
+      <c r="AU28" s="14"/>
+      <c r="AV28" s="14"/>
+      <c r="AW28" s="14"/>
+      <c r="AX28" s="14"/>
+      <c r="AY28" s="14"/>
+      <c r="AZ28" s="14"/>
+      <c r="BA28" s="14"/>
+      <c r="BB28" s="14"/>
+      <c r="BC28" s="14"/>
+      <c r="BD28" s="14">
+        <v>0</v>
+      </c>
+      <c r="BE28" s="14">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
+      <c r="AE29" s="14"/>
+      <c r="AF29" s="14"/>
+      <c r="AG29" s="14"/>
+      <c r="AH29" s="14"/>
+      <c r="AI29" s="14"/>
+      <c r="AJ29" s="14"/>
+      <c r="AK29" s="14"/>
+      <c r="AL29" s="14"/>
+      <c r="AM29" s="14"/>
+      <c r="AN29" s="14"/>
+      <c r="AO29" s="14"/>
+      <c r="AP29" s="14"/>
+      <c r="AQ29" s="14"/>
+      <c r="AR29" s="14"/>
+      <c r="AS29" s="14"/>
+      <c r="AT29" s="14"/>
+      <c r="AU29" s="14"/>
+      <c r="AV29" s="14"/>
+      <c r="AW29" s="14"/>
+      <c r="AX29" s="14"/>
+      <c r="AY29" s="14"/>
+      <c r="AZ29" s="14"/>
+      <c r="BA29" s="14"/>
+      <c r="BB29" s="14"/>
+      <c r="BC29" s="14"/>
+      <c r="BD29" s="14">
+        <v>8</v>
+      </c>
+      <c r="BE29" s="14">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="14"/>
+      <c r="AE30" s="14"/>
+      <c r="AF30" s="14"/>
+      <c r="AG30" s="14"/>
+      <c r="AH30" s="14"/>
+      <c r="AI30" s="14"/>
+      <c r="AJ30" s="14"/>
+      <c r="AK30" s="14"/>
+      <c r="AL30" s="14"/>
+      <c r="AM30" s="14"/>
+      <c r="AN30" s="14"/>
+      <c r="AO30" s="14"/>
+      <c r="AP30" s="14"/>
+      <c r="AQ30" s="14"/>
+      <c r="AR30" s="14"/>
+      <c r="AS30" s="14"/>
+      <c r="AT30" s="14"/>
+      <c r="AU30" s="14"/>
+      <c r="AV30" s="14"/>
+      <c r="AW30" s="14"/>
+      <c r="AX30" s="14"/>
+      <c r="AY30" s="14"/>
+      <c r="AZ30" s="14"/>
+      <c r="BA30" s="14"/>
+      <c r="BB30" s="14"/>
+      <c r="BC30" s="14"/>
+      <c r="BD30" s="14">
+        <v>21</v>
+      </c>
+      <c r="BE30" s="14">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="14"/>
+      <c r="AF31" s="14"/>
+      <c r="AG31" s="14"/>
+      <c r="AH31" s="14"/>
+      <c r="AI31" s="14"/>
+      <c r="AJ31" s="14"/>
+      <c r="AK31" s="14"/>
+      <c r="AL31" s="14"/>
+      <c r="AM31" s="14"/>
+      <c r="AN31" s="14"/>
+      <c r="AO31" s="14"/>
+      <c r="AP31" s="14"/>
+      <c r="AQ31" s="14"/>
+      <c r="AR31" s="14"/>
+      <c r="AS31" s="14"/>
+      <c r="AT31" s="14"/>
+      <c r="AU31" s="14"/>
+      <c r="AV31" s="14"/>
+      <c r="AW31" s="14"/>
+      <c r="AX31" s="14"/>
+      <c r="AY31" s="14"/>
+      <c r="AZ31" s="14"/>
+      <c r="BA31" s="14"/>
+      <c r="BB31" s="14"/>
+      <c r="BC31" s="14"/>
+      <c r="BD31" s="14">
+        <v>2</v>
+      </c>
+      <c r="BE31" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="14"/>
+      <c r="AF32" s="14"/>
+      <c r="AG32" s="14"/>
+      <c r="AH32" s="14"/>
+      <c r="AI32" s="14"/>
+      <c r="AJ32" s="14"/>
+      <c r="AK32" s="14"/>
+      <c r="AL32" s="14"/>
+      <c r="AM32" s="14"/>
+      <c r="AN32" s="14"/>
+      <c r="AO32" s="14"/>
+      <c r="AP32" s="14"/>
+      <c r="AQ32" s="14"/>
+      <c r="AR32" s="14"/>
+      <c r="AS32" s="14"/>
+      <c r="AT32" s="14"/>
+      <c r="AU32" s="14"/>
+      <c r="AV32" s="14"/>
+      <c r="AW32" s="14"/>
+      <c r="AX32" s="14"/>
+      <c r="AY32" s="14"/>
+      <c r="AZ32" s="14"/>
+      <c r="BA32" s="14"/>
+      <c r="BB32" s="14"/>
+      <c r="BC32" s="14"/>
+      <c r="BD32" s="14">
+        <v>0</v>
+      </c>
+      <c r="BE32" s="14">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
+      <c r="AF33" s="14"/>
+      <c r="AG33" s="14"/>
+      <c r="AH33" s="14"/>
+      <c r="AI33" s="14"/>
+      <c r="AJ33" s="14"/>
+      <c r="AK33" s="14"/>
+      <c r="AL33" s="14"/>
+      <c r="AM33" s="14"/>
+      <c r="AN33" s="14"/>
+      <c r="AO33" s="14"/>
+      <c r="AP33" s="14"/>
+      <c r="AQ33" s="14"/>
+      <c r="AR33" s="14"/>
+      <c r="AS33" s="14"/>
+      <c r="AT33" s="14"/>
+      <c r="AU33" s="14"/>
+      <c r="AV33" s="14"/>
+      <c r="AW33" s="14"/>
+      <c r="AX33" s="14"/>
+      <c r="AY33" s="14"/>
+      <c r="AZ33" s="14"/>
+      <c r="BA33" s="14"/>
+      <c r="BB33" s="14"/>
+      <c r="BC33" s="14"/>
+      <c r="BD33" s="14">
+        <v>23</v>
+      </c>
+      <c r="BE33" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="14"/>
+      <c r="AE34" s="14"/>
+      <c r="AF34" s="14"/>
+      <c r="AG34" s="14"/>
+      <c r="AH34" s="14"/>
+      <c r="AI34" s="14"/>
+      <c r="AJ34" s="14"/>
+      <c r="AK34" s="14"/>
+      <c r="AL34" s="14"/>
+      <c r="AM34" s="14"/>
+      <c r="AN34" s="14"/>
+      <c r="AO34" s="14"/>
+      <c r="AP34" s="14"/>
+      <c r="AQ34" s="14"/>
+      <c r="AR34" s="14"/>
+      <c r="AS34" s="14"/>
+      <c r="AT34" s="14"/>
+      <c r="AU34" s="14"/>
+      <c r="AV34" s="14"/>
+      <c r="AW34" s="14"/>
+      <c r="AX34" s="14"/>
+      <c r="AY34" s="14"/>
+      <c r="AZ34" s="14"/>
+      <c r="BA34" s="14"/>
+      <c r="BB34" s="14"/>
+      <c r="BC34" s="14"/>
+      <c r="BD34" s="14">
+        <v>18</v>
+      </c>
+      <c r="BE34" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="14"/>
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="14"/>
+      <c r="AA35" s="14"/>
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="14"/>
+      <c r="AD35" s="14"/>
+      <c r="AE35" s="14"/>
+      <c r="AF35" s="14"/>
+      <c r="AG35" s="14"/>
+      <c r="AH35" s="14"/>
+      <c r="AI35" s="14"/>
+      <c r="AJ35" s="14"/>
+      <c r="AK35" s="14"/>
+      <c r="AL35" s="14"/>
+      <c r="AM35" s="14"/>
+      <c r="AN35" s="14"/>
+      <c r="AO35" s="14"/>
+      <c r="AP35" s="14"/>
+      <c r="AQ35" s="14"/>
+      <c r="AR35" s="14"/>
+      <c r="AS35" s="14"/>
+      <c r="AT35" s="14"/>
+      <c r="AU35" s="14"/>
+      <c r="AV35" s="14"/>
+      <c r="AW35" s="14"/>
+      <c r="AX35" s="14"/>
+      <c r="AY35" s="14"/>
+      <c r="AZ35" s="14"/>
+      <c r="BA35" s="14"/>
+      <c r="BB35" s="14"/>
+      <c r="BC35" s="14"/>
+      <c r="BD35" s="14">
+        <v>17</v>
+      </c>
+      <c r="BE35" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="14"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
+      <c r="Y36" s="14"/>
+      <c r="Z36" s="14"/>
+      <c r="AA36" s="14"/>
+      <c r="AB36" s="14"/>
+      <c r="AC36" s="14"/>
+      <c r="AD36" s="14"/>
+      <c r="AE36" s="14"/>
+      <c r="AF36" s="14"/>
+      <c r="AG36" s="14"/>
+      <c r="AH36" s="14"/>
+      <c r="AI36" s="14"/>
+      <c r="AJ36" s="14"/>
+      <c r="AK36" s="14"/>
+      <c r="AL36" s="14"/>
+      <c r="AM36" s="14"/>
+      <c r="AN36" s="14"/>
+      <c r="AO36" s="14"/>
+      <c r="AP36" s="14"/>
+      <c r="AQ36" s="14"/>
+      <c r="AR36" s="14"/>
+      <c r="AS36" s="14"/>
+      <c r="AT36" s="14"/>
+      <c r="AU36" s="14"/>
+      <c r="AV36" s="14"/>
+      <c r="AW36" s="14"/>
+      <c r="AX36" s="14"/>
+      <c r="AY36" s="14"/>
+      <c r="AZ36" s="14"/>
+      <c r="BA36" s="14"/>
+      <c r="BB36" s="14"/>
+      <c r="BC36" s="14"/>
+      <c r="BD36" s="14">
+        <v>17</v>
+      </c>
+      <c r="BE36" s="14">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="14"/>
+      <c r="AF37" s="14"/>
+      <c r="AG37" s="14"/>
+      <c r="AH37" s="14"/>
+      <c r="AI37" s="14"/>
+      <c r="AJ37" s="14"/>
+      <c r="AK37" s="14"/>
+      <c r="AL37" s="14"/>
+      <c r="AM37" s="14"/>
+      <c r="AN37" s="14"/>
+      <c r="AO37" s="14"/>
+      <c r="AP37" s="14"/>
+      <c r="AQ37" s="14"/>
+      <c r="AR37" s="14"/>
+      <c r="AS37" s="14"/>
+      <c r="AT37" s="14"/>
+      <c r="AU37" s="14"/>
+      <c r="AV37" s="14"/>
+      <c r="AW37" s="14"/>
+      <c r="AX37" s="14"/>
+      <c r="AY37" s="14"/>
+      <c r="AZ37" s="14"/>
+      <c r="BA37" s="14"/>
+      <c r="BB37" s="14"/>
+      <c r="BC37" s="14"/>
+      <c r="BD37" s="14">
+        <v>18</v>
+      </c>
+      <c r="BE37" s="14">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Vanya\inf\FAKT_INFORMATICS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tmp\FAKT_INFORMATICS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA38F044-EB03-4404-B27D-7481AF7E621D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBA3303-CE0D-4055-9209-E2E29B57B21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{9546C0DC-CDD5-4F7B-8A2F-88672275CD35}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{9546C0DC-CDD5-4F7B-8A2F-88672275CD35}"/>
   </bookViews>
   <sheets>
     <sheet name="посещения" sheetId="1" r:id="rId1"/>
@@ -249,7 +249,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,6 +265,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -354,7 +360,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -370,6 +376,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -389,9 +396,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -429,7 +436,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -535,7 +542,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -677,7 +684,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1574,13 +1581,13 @@
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="12">
+      <c r="G4" s="15">
         <v>8</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="13">
-        <f t="shared" ref="J4:J19" si="0">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
+        <f t="shared" ref="J4:J6" si="0">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
         <v>3</v>
       </c>
     </row>
@@ -1631,14 +1638,14 @@
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
-      <c r="G7" s="12">
-        <v>5</v>
+      <c r="G7" s="15">
+        <v>8</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="13">
-        <f>MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
-        <v>2</v>
+        <f t="shared" ref="J7:J16" si="1">MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1658,7 +1665,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="13">
-        <f>MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -1679,7 +1686,7 @@
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13">
-        <f>MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -1696,7 +1703,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="13">
-        <f>MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1713,7 +1720,7 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13">
-        <f>MIN(10, ROUNDUP((B11+C11+D11+E11+F11)/3+G11/3+H11/3+I11,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1734,7 +1741,7 @@
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
       <c r="J12" s="13">
-        <f>MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -1753,7 +1760,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="13">
-        <f>MIN(10, ROUNDUP((B13+C13+D13+E13+F13)/3+G13/3+H13/3+I13,0))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -1774,7 +1781,7 @@
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13">
-        <f>MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -1787,13 +1794,13 @@
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="12">
+      <c r="G15" s="15">
         <v>9</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="13">
-        <f>MIN(10, ROUNDUP((B15+C15+D15+E15+F15)/3+G15/3+H15/3+I15,0))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -1814,7 +1821,7 @@
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
       <c r="J16" s="13">
-        <f>MIN(10, ROUNDUP((B16+C16+D16+E16+F16)/3+G16/3+H16/3+I16,0))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -222,19 +222,19 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -360,7 +360,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -370,15 +370,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,11 +406,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -426,7 +426,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -438,7 +438,7 @@
     <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
-    <cellStyle name="Обычный 2" xfId="20" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -1496,7 +1496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
@@ -1504,7 +1504,9 @@
         <v>1</v>
       </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="D8" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="n">
@@ -1629,7 +1631,9 @@
       <c r="B14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="13"/>
+      <c r="C14" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="D14" s="13" t="n">
         <v>2</v>
       </c>
@@ -1642,7 +1646,7 @@
       <c r="I14" s="13"/>
       <c r="J14" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1549,7 +1549,9 @@
       <c r="B10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="12"/>
+      <c r="C10" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="D10" s="12" t="n">
         <v>2</v>
       </c>

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1457,7 +1457,9 @@
       <c r="B6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="12"/>
+      <c r="C6" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="D6" s="12" t="n">
         <v>2</v>
       </c>
@@ -1557,12 +1559,14 @@
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="12" t="n">
+        <v>7</v>
+      </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1574,12 +1578,14 @@
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="G11" s="13" t="n">
+        <v>10</v>
+      </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B11+C11+D11+E11+F11)/3+G11/3+H11/3+I11,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1679,7 +1685,9 @@
       <c r="B16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="13"/>
+      <c r="C16" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="D16" s="13" t="n">
         <v>2</v>
       </c>

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -237,7 +237,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,12 +254,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0D9"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor rgb="FF800000"/>
       </patternFill>
     </fill>
   </fills>
@@ -365,7 +359,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -422,10 +416,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -444,7 +434,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1379,7 +1369,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
@@ -1404,40 +1394,42 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="D4" s="12" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13" t="n">
-        <v>2</v>
-      </c>
+      <c r="C5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13" t="n">
@@ -1450,7 +1442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
@@ -1475,27 +1467,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="D7" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="12"/>
+      <c r="E7" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="F7" s="12"/>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1509,7 +1505,9 @@
       <c r="D8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="n">
         <v>9</v>
@@ -1518,21 +1516,25 @@
       <c r="I8" s="12"/>
       <c r="J8" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="13"/>
+      <c r="C9" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="D9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="13"/>
+      <c r="E9" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="n">
         <v>6</v>
@@ -1541,10 +1543,10 @@
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
@@ -1554,9 +1556,7 @@
       <c r="C10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>2</v>
-      </c>
+      <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="n">
@@ -1566,10 +1566,10 @@
       <c r="I10" s="12"/>
       <c r="J10" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -1588,18 +1588,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>42</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="13"/>
+      <c r="C12" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="D12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="13"/>
+      <c r="E12" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="n">
         <v>7</v>
@@ -1608,10 +1612,10 @@
       <c r="I12" s="13"/>
       <c r="J12" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
         <v>43</v>
       </c>
@@ -1632,7 +1636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>44</v>
       </c>
@@ -1645,7 +1649,9 @@
       <c r="D14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="n">
         <v>8</v>
@@ -1654,21 +1660,21 @@
       <c r="I14" s="13"/>
       <c r="J14" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12" t="n">
-        <v>2</v>
-      </c>
+      <c r="C15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H15" s="12"/>
@@ -1678,7 +1684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
         <v>46</v>
       </c>
@@ -1688,9 +1694,7 @@
       <c r="C16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="n">
-        <v>2</v>
-      </c>
+      <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13" t="n">
@@ -1714,734 +1718,734 @@
       <c r="P19" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="15"/>
-      <c r="AA26" s="15"/>
-      <c r="AB26" s="15"/>
-      <c r="AC26" s="15"/>
-      <c r="AD26" s="15"/>
-      <c r="AE26" s="15"/>
-      <c r="AF26" s="15"/>
-      <c r="AG26" s="15"/>
-      <c r="AH26" s="15"/>
-      <c r="AI26" s="15"/>
-      <c r="AJ26" s="15"/>
-      <c r="AK26" s="15"/>
-      <c r="AL26" s="15"/>
-      <c r="AM26" s="15"/>
-      <c r="AN26" s="15"/>
-      <c r="AO26" s="15"/>
-      <c r="AP26" s="15"/>
-      <c r="AQ26" s="15"/>
-      <c r="AR26" s="15"/>
-      <c r="AS26" s="15"/>
-      <c r="AT26" s="15"/>
-      <c r="AU26" s="15"/>
-      <c r="AV26" s="15"/>
-      <c r="AW26" s="15"/>
-      <c r="AX26" s="15"/>
-      <c r="AY26" s="15"/>
-      <c r="AZ26" s="15"/>
-      <c r="BA26" s="15"/>
-      <c r="BB26" s="15"/>
-      <c r="BC26" s="15"/>
-      <c r="BD26" s="15" t="n">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+      <c r="AE26" s="14"/>
+      <c r="AF26" s="14"/>
+      <c r="AG26" s="14"/>
+      <c r="AH26" s="14"/>
+      <c r="AI26" s="14"/>
+      <c r="AJ26" s="14"/>
+      <c r="AK26" s="14"/>
+      <c r="AL26" s="14"/>
+      <c r="AM26" s="14"/>
+      <c r="AN26" s="14"/>
+      <c r="AO26" s="14"/>
+      <c r="AP26" s="14"/>
+      <c r="AQ26" s="14"/>
+      <c r="AR26" s="14"/>
+      <c r="AS26" s="14"/>
+      <c r="AT26" s="14"/>
+      <c r="AU26" s="14"/>
+      <c r="AV26" s="14"/>
+      <c r="AW26" s="14"/>
+      <c r="AX26" s="14"/>
+      <c r="AY26" s="14"/>
+      <c r="AZ26" s="14"/>
+      <c r="BA26" s="14"/>
+      <c r="BB26" s="14"/>
+      <c r="BC26" s="14"/>
+      <c r="BD26" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE26" s="15" t="n">
+      <c r="BE26" s="14" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="15"/>
-      <c r="AG27" s="15"/>
-      <c r="AH27" s="15"/>
-      <c r="AI27" s="15"/>
-      <c r="AJ27" s="15"/>
-      <c r="AK27" s="15"/>
-      <c r="AL27" s="15"/>
-      <c r="AM27" s="15"/>
-      <c r="AN27" s="15"/>
-      <c r="AO27" s="15"/>
-      <c r="AP27" s="15"/>
-      <c r="AQ27" s="15"/>
-      <c r="AR27" s="15"/>
-      <c r="AS27" s="15"/>
-      <c r="AT27" s="15"/>
-      <c r="AU27" s="15"/>
-      <c r="AV27" s="15"/>
-      <c r="AW27" s="15"/>
-      <c r="AX27" s="15"/>
-      <c r="AY27" s="15"/>
-      <c r="AZ27" s="15"/>
-      <c r="BA27" s="15"/>
-      <c r="BB27" s="15"/>
-      <c r="BC27" s="15"/>
-      <c r="BD27" s="15" t="n">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
+      <c r="AE27" s="14"/>
+      <c r="AF27" s="14"/>
+      <c r="AG27" s="14"/>
+      <c r="AH27" s="14"/>
+      <c r="AI27" s="14"/>
+      <c r="AJ27" s="14"/>
+      <c r="AK27" s="14"/>
+      <c r="AL27" s="14"/>
+      <c r="AM27" s="14"/>
+      <c r="AN27" s="14"/>
+      <c r="AO27" s="14"/>
+      <c r="AP27" s="14"/>
+      <c r="AQ27" s="14"/>
+      <c r="AR27" s="14"/>
+      <c r="AS27" s="14"/>
+      <c r="AT27" s="14"/>
+      <c r="AU27" s="14"/>
+      <c r="AV27" s="14"/>
+      <c r="AW27" s="14"/>
+      <c r="AX27" s="14"/>
+      <c r="AY27" s="14"/>
+      <c r="AZ27" s="14"/>
+      <c r="BA27" s="14"/>
+      <c r="BB27" s="14"/>
+      <c r="BC27" s="14"/>
+      <c r="BD27" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="BE27" s="15" t="n">
+      <c r="BE27" s="14" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="15"/>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
-      <c r="AB28" s="15"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="15"/>
-      <c r="AG28" s="15"/>
-      <c r="AH28" s="15"/>
-      <c r="AI28" s="15"/>
-      <c r="AJ28" s="15"/>
-      <c r="AK28" s="15"/>
-      <c r="AL28" s="15"/>
-      <c r="AM28" s="15"/>
-      <c r="AN28" s="15"/>
-      <c r="AO28" s="15"/>
-      <c r="AP28" s="15"/>
-      <c r="AQ28" s="15"/>
-      <c r="AR28" s="15"/>
-      <c r="AS28" s="15"/>
-      <c r="AT28" s="15"/>
-      <c r="AU28" s="15"/>
-      <c r="AV28" s="15"/>
-      <c r="AW28" s="15"/>
-      <c r="AX28" s="15"/>
-      <c r="AY28" s="15"/>
-      <c r="AZ28" s="15"/>
-      <c r="BA28" s="15"/>
-      <c r="BB28" s="15"/>
-      <c r="BC28" s="15"/>
-      <c r="BD28" s="15" t="n">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
+      <c r="AE28" s="14"/>
+      <c r="AF28" s="14"/>
+      <c r="AG28" s="14"/>
+      <c r="AH28" s="14"/>
+      <c r="AI28" s="14"/>
+      <c r="AJ28" s="14"/>
+      <c r="AK28" s="14"/>
+      <c r="AL28" s="14"/>
+      <c r="AM28" s="14"/>
+      <c r="AN28" s="14"/>
+      <c r="AO28" s="14"/>
+      <c r="AP28" s="14"/>
+      <c r="AQ28" s="14"/>
+      <c r="AR28" s="14"/>
+      <c r="AS28" s="14"/>
+      <c r="AT28" s="14"/>
+      <c r="AU28" s="14"/>
+      <c r="AV28" s="14"/>
+      <c r="AW28" s="14"/>
+      <c r="AX28" s="14"/>
+      <c r="AY28" s="14"/>
+      <c r="AZ28" s="14"/>
+      <c r="BA28" s="14"/>
+      <c r="BB28" s="14"/>
+      <c r="BC28" s="14"/>
+      <c r="BD28" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BE28" s="15" t="n">
+      <c r="BE28" s="14" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="15"/>
-      <c r="S29" s="15"/>
-      <c r="T29" s="15"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="15"/>
-      <c r="AB29" s="15"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
-      <c r="AE29" s="15"/>
-      <c r="AF29" s="15"/>
-      <c r="AG29" s="15"/>
-      <c r="AH29" s="15"/>
-      <c r="AI29" s="15"/>
-      <c r="AJ29" s="15"/>
-      <c r="AK29" s="15"/>
-      <c r="AL29" s="15"/>
-      <c r="AM29" s="15"/>
-      <c r="AN29" s="15"/>
-      <c r="AO29" s="15"/>
-      <c r="AP29" s="15"/>
-      <c r="AQ29" s="15"/>
-      <c r="AR29" s="15"/>
-      <c r="AS29" s="15"/>
-      <c r="AT29" s="15"/>
-      <c r="AU29" s="15"/>
-      <c r="AV29" s="15"/>
-      <c r="AW29" s="15"/>
-      <c r="AX29" s="15"/>
-      <c r="AY29" s="15"/>
-      <c r="AZ29" s="15"/>
-      <c r="BA29" s="15"/>
-      <c r="BB29" s="15"/>
-      <c r="BC29" s="15"/>
-      <c r="BD29" s="15" t="n">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
+      <c r="AE29" s="14"/>
+      <c r="AF29" s="14"/>
+      <c r="AG29" s="14"/>
+      <c r="AH29" s="14"/>
+      <c r="AI29" s="14"/>
+      <c r="AJ29" s="14"/>
+      <c r="AK29" s="14"/>
+      <c r="AL29" s="14"/>
+      <c r="AM29" s="14"/>
+      <c r="AN29" s="14"/>
+      <c r="AO29" s="14"/>
+      <c r="AP29" s="14"/>
+      <c r="AQ29" s="14"/>
+      <c r="AR29" s="14"/>
+      <c r="AS29" s="14"/>
+      <c r="AT29" s="14"/>
+      <c r="AU29" s="14"/>
+      <c r="AV29" s="14"/>
+      <c r="AW29" s="14"/>
+      <c r="AX29" s="14"/>
+      <c r="AY29" s="14"/>
+      <c r="AZ29" s="14"/>
+      <c r="BA29" s="14"/>
+      <c r="BB29" s="14"/>
+      <c r="BC29" s="14"/>
+      <c r="BD29" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="BE29" s="15" t="n">
+      <c r="BE29" s="14" t="n">
         <v>31</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="15"/>
-      <c r="S30" s="15"/>
-      <c r="T30" s="15"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="15"/>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="Y30" s="15"/>
-      <c r="Z30" s="15"/>
-      <c r="AA30" s="15"/>
-      <c r="AB30" s="15"/>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="15"/>
-      <c r="AE30" s="15"/>
-      <c r="AF30" s="15"/>
-      <c r="AG30" s="15"/>
-      <c r="AH30" s="15"/>
-      <c r="AI30" s="15"/>
-      <c r="AJ30" s="15"/>
-      <c r="AK30" s="15"/>
-      <c r="AL30" s="15"/>
-      <c r="AM30" s="15"/>
-      <c r="AN30" s="15"/>
-      <c r="AO30" s="15"/>
-      <c r="AP30" s="15"/>
-      <c r="AQ30" s="15"/>
-      <c r="AR30" s="15"/>
-      <c r="AS30" s="15"/>
-      <c r="AT30" s="15"/>
-      <c r="AU30" s="15"/>
-      <c r="AV30" s="15"/>
-      <c r="AW30" s="15"/>
-      <c r="AX30" s="15"/>
-      <c r="AY30" s="15"/>
-      <c r="AZ30" s="15"/>
-      <c r="BA30" s="15"/>
-      <c r="BB30" s="15"/>
-      <c r="BC30" s="15"/>
-      <c r="BD30" s="15" t="n">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="14"/>
+      <c r="AE30" s="14"/>
+      <c r="AF30" s="14"/>
+      <c r="AG30" s="14"/>
+      <c r="AH30" s="14"/>
+      <c r="AI30" s="14"/>
+      <c r="AJ30" s="14"/>
+      <c r="AK30" s="14"/>
+      <c r="AL30" s="14"/>
+      <c r="AM30" s="14"/>
+      <c r="AN30" s="14"/>
+      <c r="AO30" s="14"/>
+      <c r="AP30" s="14"/>
+      <c r="AQ30" s="14"/>
+      <c r="AR30" s="14"/>
+      <c r="AS30" s="14"/>
+      <c r="AT30" s="14"/>
+      <c r="AU30" s="14"/>
+      <c r="AV30" s="14"/>
+      <c r="AW30" s="14"/>
+      <c r="AX30" s="14"/>
+      <c r="AY30" s="14"/>
+      <c r="AZ30" s="14"/>
+      <c r="BA30" s="14"/>
+      <c r="BB30" s="14"/>
+      <c r="BC30" s="14"/>
+      <c r="BD30" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="BE30" s="15" t="n">
+      <c r="BE30" s="14" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="15"/>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="15"/>
-      <c r="AA31" s="15"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
-      <c r="AE31" s="15"/>
-      <c r="AF31" s="15"/>
-      <c r="AG31" s="15"/>
-      <c r="AH31" s="15"/>
-      <c r="AI31" s="15"/>
-      <c r="AJ31" s="15"/>
-      <c r="AK31" s="15"/>
-      <c r="AL31" s="15"/>
-      <c r="AM31" s="15"/>
-      <c r="AN31" s="15"/>
-      <c r="AO31" s="15"/>
-      <c r="AP31" s="15"/>
-      <c r="AQ31" s="15"/>
-      <c r="AR31" s="15"/>
-      <c r="AS31" s="15"/>
-      <c r="AT31" s="15"/>
-      <c r="AU31" s="15"/>
-      <c r="AV31" s="15"/>
-      <c r="AW31" s="15"/>
-      <c r="AX31" s="15"/>
-      <c r="AY31" s="15"/>
-      <c r="AZ31" s="15"/>
-      <c r="BA31" s="15"/>
-      <c r="BB31" s="15"/>
-      <c r="BC31" s="15"/>
-      <c r="BD31" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE31" s="15" t="n">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="14"/>
+      <c r="AF31" s="14"/>
+      <c r="AG31" s="14"/>
+      <c r="AH31" s="14"/>
+      <c r="AI31" s="14"/>
+      <c r="AJ31" s="14"/>
+      <c r="AK31" s="14"/>
+      <c r="AL31" s="14"/>
+      <c r="AM31" s="14"/>
+      <c r="AN31" s="14"/>
+      <c r="AO31" s="14"/>
+      <c r="AP31" s="14"/>
+      <c r="AQ31" s="14"/>
+      <c r="AR31" s="14"/>
+      <c r="AS31" s="14"/>
+      <c r="AT31" s="14"/>
+      <c r="AU31" s="14"/>
+      <c r="AV31" s="14"/>
+      <c r="AW31" s="14"/>
+      <c r="AX31" s="14"/>
+      <c r="AY31" s="14"/>
+      <c r="AZ31" s="14"/>
+      <c r="BA31" s="14"/>
+      <c r="BB31" s="14"/>
+      <c r="BC31" s="14"/>
+      <c r="BD31" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE31" s="14" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="15"/>
-      <c r="U32" s="15"/>
-      <c r="V32" s="15"/>
-      <c r="W32" s="15"/>
-      <c r="X32" s="15"/>
-      <c r="Y32" s="15"/>
-      <c r="Z32" s="15"/>
-      <c r="AA32" s="15"/>
-      <c r="AB32" s="15"/>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="15"/>
-      <c r="AE32" s="15"/>
-      <c r="AF32" s="15"/>
-      <c r="AG32" s="15"/>
-      <c r="AH32" s="15"/>
-      <c r="AI32" s="15"/>
-      <c r="AJ32" s="15"/>
-      <c r="AK32" s="15"/>
-      <c r="AL32" s="15"/>
-      <c r="AM32" s="15"/>
-      <c r="AN32" s="15"/>
-      <c r="AO32" s="15"/>
-      <c r="AP32" s="15"/>
-      <c r="AQ32" s="15"/>
-      <c r="AR32" s="15"/>
-      <c r="AS32" s="15"/>
-      <c r="AT32" s="15"/>
-      <c r="AU32" s="15"/>
-      <c r="AV32" s="15"/>
-      <c r="AW32" s="15"/>
-      <c r="AX32" s="15"/>
-      <c r="AY32" s="15"/>
-      <c r="AZ32" s="15"/>
-      <c r="BA32" s="15"/>
-      <c r="BB32" s="15"/>
-      <c r="BC32" s="15"/>
-      <c r="BD32" s="15" t="n">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="14"/>
+      <c r="AF32" s="14"/>
+      <c r="AG32" s="14"/>
+      <c r="AH32" s="14"/>
+      <c r="AI32" s="14"/>
+      <c r="AJ32" s="14"/>
+      <c r="AK32" s="14"/>
+      <c r="AL32" s="14"/>
+      <c r="AM32" s="14"/>
+      <c r="AN32" s="14"/>
+      <c r="AO32" s="14"/>
+      <c r="AP32" s="14"/>
+      <c r="AQ32" s="14"/>
+      <c r="AR32" s="14"/>
+      <c r="AS32" s="14"/>
+      <c r="AT32" s="14"/>
+      <c r="AU32" s="14"/>
+      <c r="AV32" s="14"/>
+      <c r="AW32" s="14"/>
+      <c r="AX32" s="14"/>
+      <c r="AY32" s="14"/>
+      <c r="AZ32" s="14"/>
+      <c r="BA32" s="14"/>
+      <c r="BB32" s="14"/>
+      <c r="BC32" s="14"/>
+      <c r="BD32" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BE32" s="15" t="n">
+      <c r="BE32" s="14" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="15"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="15"/>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
-      <c r="Y33" s="15"/>
-      <c r="Z33" s="15"/>
-      <c r="AA33" s="15"/>
-      <c r="AB33" s="15"/>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="15"/>
-      <c r="AE33" s="15"/>
-      <c r="AF33" s="15"/>
-      <c r="AG33" s="15"/>
-      <c r="AH33" s="15"/>
-      <c r="AI33" s="15"/>
-      <c r="AJ33" s="15"/>
-      <c r="AK33" s="15"/>
-      <c r="AL33" s="15"/>
-      <c r="AM33" s="15"/>
-      <c r="AN33" s="15"/>
-      <c r="AO33" s="15"/>
-      <c r="AP33" s="15"/>
-      <c r="AQ33" s="15"/>
-      <c r="AR33" s="15"/>
-      <c r="AS33" s="15"/>
-      <c r="AT33" s="15"/>
-      <c r="AU33" s="15"/>
-      <c r="AV33" s="15"/>
-      <c r="AW33" s="15"/>
-      <c r="AX33" s="15"/>
-      <c r="AY33" s="15"/>
-      <c r="AZ33" s="15"/>
-      <c r="BA33" s="15"/>
-      <c r="BB33" s="15"/>
-      <c r="BC33" s="15"/>
-      <c r="BD33" s="15" t="n">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
+      <c r="AF33" s="14"/>
+      <c r="AG33" s="14"/>
+      <c r="AH33" s="14"/>
+      <c r="AI33" s="14"/>
+      <c r="AJ33" s="14"/>
+      <c r="AK33" s="14"/>
+      <c r="AL33" s="14"/>
+      <c r="AM33" s="14"/>
+      <c r="AN33" s="14"/>
+      <c r="AO33" s="14"/>
+      <c r="AP33" s="14"/>
+      <c r="AQ33" s="14"/>
+      <c r="AR33" s="14"/>
+      <c r="AS33" s="14"/>
+      <c r="AT33" s="14"/>
+      <c r="AU33" s="14"/>
+      <c r="AV33" s="14"/>
+      <c r="AW33" s="14"/>
+      <c r="AX33" s="14"/>
+      <c r="AY33" s="14"/>
+      <c r="AZ33" s="14"/>
+      <c r="BA33" s="14"/>
+      <c r="BB33" s="14"/>
+      <c r="BC33" s="14"/>
+      <c r="BD33" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="BE33" s="15" t="n">
+      <c r="BE33" s="14" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="15"/>
-      <c r="T34" s="15"/>
-      <c r="U34" s="15"/>
-      <c r="V34" s="15"/>
-      <c r="W34" s="15"/>
-      <c r="X34" s="15"/>
-      <c r="Y34" s="15"/>
-      <c r="Z34" s="15"/>
-      <c r="AA34" s="15"/>
-      <c r="AB34" s="15"/>
-      <c r="AC34" s="15"/>
-      <c r="AD34" s="15"/>
-      <c r="AE34" s="15"/>
-      <c r="AF34" s="15"/>
-      <c r="AG34" s="15"/>
-      <c r="AH34" s="15"/>
-      <c r="AI34" s="15"/>
-      <c r="AJ34" s="15"/>
-      <c r="AK34" s="15"/>
-      <c r="AL34" s="15"/>
-      <c r="AM34" s="15"/>
-      <c r="AN34" s="15"/>
-      <c r="AO34" s="15"/>
-      <c r="AP34" s="15"/>
-      <c r="AQ34" s="15"/>
-      <c r="AR34" s="15"/>
-      <c r="AS34" s="15"/>
-      <c r="AT34" s="15"/>
-      <c r="AU34" s="15"/>
-      <c r="AV34" s="15"/>
-      <c r="AW34" s="15"/>
-      <c r="AX34" s="15"/>
-      <c r="AY34" s="15"/>
-      <c r="AZ34" s="15"/>
-      <c r="BA34" s="15"/>
-      <c r="BB34" s="15"/>
-      <c r="BC34" s="15"/>
-      <c r="BD34" s="15" t="n">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="14"/>
+      <c r="AE34" s="14"/>
+      <c r="AF34" s="14"/>
+      <c r="AG34" s="14"/>
+      <c r="AH34" s="14"/>
+      <c r="AI34" s="14"/>
+      <c r="AJ34" s="14"/>
+      <c r="AK34" s="14"/>
+      <c r="AL34" s="14"/>
+      <c r="AM34" s="14"/>
+      <c r="AN34" s="14"/>
+      <c r="AO34" s="14"/>
+      <c r="AP34" s="14"/>
+      <c r="AQ34" s="14"/>
+      <c r="AR34" s="14"/>
+      <c r="AS34" s="14"/>
+      <c r="AT34" s="14"/>
+      <c r="AU34" s="14"/>
+      <c r="AV34" s="14"/>
+      <c r="AW34" s="14"/>
+      <c r="AX34" s="14"/>
+      <c r="AY34" s="14"/>
+      <c r="AZ34" s="14"/>
+      <c r="BA34" s="14"/>
+      <c r="BB34" s="14"/>
+      <c r="BC34" s="14"/>
+      <c r="BD34" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE34" s="15" t="n">
+      <c r="BE34" s="14" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="15"/>
-      <c r="S35" s="15"/>
-      <c r="T35" s="15"/>
-      <c r="U35" s="15"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
-      <c r="Y35" s="15"/>
-      <c r="Z35" s="15"/>
-      <c r="AA35" s="15"/>
-      <c r="AB35" s="15"/>
-      <c r="AC35" s="15"/>
-      <c r="AD35" s="15"/>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="15"/>
-      <c r="AG35" s="15"/>
-      <c r="AH35" s="15"/>
-      <c r="AI35" s="15"/>
-      <c r="AJ35" s="15"/>
-      <c r="AK35" s="15"/>
-      <c r="AL35" s="15"/>
-      <c r="AM35" s="15"/>
-      <c r="AN35" s="15"/>
-      <c r="AO35" s="15"/>
-      <c r="AP35" s="15"/>
-      <c r="AQ35" s="15"/>
-      <c r="AR35" s="15"/>
-      <c r="AS35" s="15"/>
-      <c r="AT35" s="15"/>
-      <c r="AU35" s="15"/>
-      <c r="AV35" s="15"/>
-      <c r="AW35" s="15"/>
-      <c r="AX35" s="15"/>
-      <c r="AY35" s="15"/>
-      <c r="AZ35" s="15"/>
-      <c r="BA35" s="15"/>
-      <c r="BB35" s="15"/>
-      <c r="BC35" s="15"/>
-      <c r="BD35" s="15" t="n">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="14"/>
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="14"/>
+      <c r="AA35" s="14"/>
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="14"/>
+      <c r="AD35" s="14"/>
+      <c r="AE35" s="14"/>
+      <c r="AF35" s="14"/>
+      <c r="AG35" s="14"/>
+      <c r="AH35" s="14"/>
+      <c r="AI35" s="14"/>
+      <c r="AJ35" s="14"/>
+      <c r="AK35" s="14"/>
+      <c r="AL35" s="14"/>
+      <c r="AM35" s="14"/>
+      <c r="AN35" s="14"/>
+      <c r="AO35" s="14"/>
+      <c r="AP35" s="14"/>
+      <c r="AQ35" s="14"/>
+      <c r="AR35" s="14"/>
+      <c r="AS35" s="14"/>
+      <c r="AT35" s="14"/>
+      <c r="AU35" s="14"/>
+      <c r="AV35" s="14"/>
+      <c r="AW35" s="14"/>
+      <c r="AX35" s="14"/>
+      <c r="AY35" s="14"/>
+      <c r="AZ35" s="14"/>
+      <c r="BA35" s="14"/>
+      <c r="BB35" s="14"/>
+      <c r="BC35" s="14"/>
+      <c r="BD35" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="BE35" s="15" t="n">
+      <c r="BE35" s="14" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36" s="15"/>
-      <c r="Z36" s="15"/>
-      <c r="AA36" s="15"/>
-      <c r="AB36" s="15"/>
-      <c r="AC36" s="15"/>
-      <c r="AD36" s="15"/>
-      <c r="AE36" s="15"/>
-      <c r="AF36" s="15"/>
-      <c r="AG36" s="15"/>
-      <c r="AH36" s="15"/>
-      <c r="AI36" s="15"/>
-      <c r="AJ36" s="15"/>
-      <c r="AK36" s="15"/>
-      <c r="AL36" s="15"/>
-      <c r="AM36" s="15"/>
-      <c r="AN36" s="15"/>
-      <c r="AO36" s="15"/>
-      <c r="AP36" s="15"/>
-      <c r="AQ36" s="15"/>
-      <c r="AR36" s="15"/>
-      <c r="AS36" s="15"/>
-      <c r="AT36" s="15"/>
-      <c r="AU36" s="15"/>
-      <c r="AV36" s="15"/>
-      <c r="AW36" s="15"/>
-      <c r="AX36" s="15"/>
-      <c r="AY36" s="15"/>
-      <c r="AZ36" s="15"/>
-      <c r="BA36" s="15"/>
-      <c r="BB36" s="15"/>
-      <c r="BC36" s="15"/>
-      <c r="BD36" s="15" t="n">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="14"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
+      <c r="Y36" s="14"/>
+      <c r="Z36" s="14"/>
+      <c r="AA36" s="14"/>
+      <c r="AB36" s="14"/>
+      <c r="AC36" s="14"/>
+      <c r="AD36" s="14"/>
+      <c r="AE36" s="14"/>
+      <c r="AF36" s="14"/>
+      <c r="AG36" s="14"/>
+      <c r="AH36" s="14"/>
+      <c r="AI36" s="14"/>
+      <c r="AJ36" s="14"/>
+      <c r="AK36" s="14"/>
+      <c r="AL36" s="14"/>
+      <c r="AM36" s="14"/>
+      <c r="AN36" s="14"/>
+      <c r="AO36" s="14"/>
+      <c r="AP36" s="14"/>
+      <c r="AQ36" s="14"/>
+      <c r="AR36" s="14"/>
+      <c r="AS36" s="14"/>
+      <c r="AT36" s="14"/>
+      <c r="AU36" s="14"/>
+      <c r="AV36" s="14"/>
+      <c r="AW36" s="14"/>
+      <c r="AX36" s="14"/>
+      <c r="AY36" s="14"/>
+      <c r="AZ36" s="14"/>
+      <c r="BA36" s="14"/>
+      <c r="BB36" s="14"/>
+      <c r="BC36" s="14"/>
+      <c r="BD36" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="BE36" s="15" t="n">
+      <c r="BE36" s="14" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="15"/>
-      <c r="Z37" s="15"/>
-      <c r="AA37" s="15"/>
-      <c r="AB37" s="15"/>
-      <c r="AC37" s="15"/>
-      <c r="AD37" s="15"/>
-      <c r="AE37" s="15"/>
-      <c r="AF37" s="15"/>
-      <c r="AG37" s="15"/>
-      <c r="AH37" s="15"/>
-      <c r="AI37" s="15"/>
-      <c r="AJ37" s="15"/>
-      <c r="AK37" s="15"/>
-      <c r="AL37" s="15"/>
-      <c r="AM37" s="15"/>
-      <c r="AN37" s="15"/>
-      <c r="AO37" s="15"/>
-      <c r="AP37" s="15"/>
-      <c r="AQ37" s="15"/>
-      <c r="AR37" s="15"/>
-      <c r="AS37" s="15"/>
-      <c r="AT37" s="15"/>
-      <c r="AU37" s="15"/>
-      <c r="AV37" s="15"/>
-      <c r="AW37" s="15"/>
-      <c r="AX37" s="15"/>
-      <c r="AY37" s="15"/>
-      <c r="AZ37" s="15"/>
-      <c r="BA37" s="15"/>
-      <c r="BB37" s="15"/>
-      <c r="BC37" s="15"/>
-      <c r="BD37" s="15" t="n">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="14"/>
+      <c r="AF37" s="14"/>
+      <c r="AG37" s="14"/>
+      <c r="AH37" s="14"/>
+      <c r="AI37" s="14"/>
+      <c r="AJ37" s="14"/>
+      <c r="AK37" s="14"/>
+      <c r="AL37" s="14"/>
+      <c r="AM37" s="14"/>
+      <c r="AN37" s="14"/>
+      <c r="AO37" s="14"/>
+      <c r="AP37" s="14"/>
+      <c r="AQ37" s="14"/>
+      <c r="AR37" s="14"/>
+      <c r="AS37" s="14"/>
+      <c r="AT37" s="14"/>
+      <c r="AU37" s="14"/>
+      <c r="AV37" s="14"/>
+      <c r="AW37" s="14"/>
+      <c r="AX37" s="14"/>
+      <c r="AY37" s="14"/>
+      <c r="AZ37" s="14"/>
+      <c r="BA37" s="14"/>
+      <c r="BB37" s="14"/>
+      <c r="BC37" s="14"/>
+      <c r="BD37" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE37" s="15" t="n">
+      <c r="BE37" s="14" t="n">
         <v>2</v>
       </c>
     </row>

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1382,7 +1382,9 @@
       <c r="D3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="F3" s="13"/>
       <c r="G3" s="13" t="n">
         <v>6</v>
@@ -1391,7 +1393,7 @@
       <c r="I3" s="13"/>
       <c r="J3" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1407,7 +1409,9 @@
       <c r="D4" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="12"/>
+      <c r="E4" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="n">
         <v>8</v>
@@ -1416,7 +1420,7 @@
       <c r="I4" s="12"/>
       <c r="J4" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1557,7 +1561,9 @@
         <v>2</v>
       </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="E10" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="n">
         <v>7</v>
@@ -1566,7 +1572,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1624,7 +1630,9 @@
       <c r="D13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="12"/>
+      <c r="E13" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="n">
         <v>6</v>
@@ -1633,7 +1641,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B13+C13+D13+E13+F13)/3+G13/3+H13/3+I13,0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1385,7 +1385,9 @@
       <c r="E3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="13"/>
+      <c r="F3" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="G3" s="13" t="n">
         <v>6</v>
       </c>
@@ -1393,7 +1395,7 @@
       <c r="I3" s="13"/>
       <c r="J3" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1412,7 +1414,9 @@
       <c r="E4" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="G4" s="12" t="n">
         <v>8</v>
       </c>
@@ -1459,8 +1463,12 @@
       <c r="D6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="E6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" s="12" t="n">
         <v>6</v>
       </c>
@@ -1468,7 +1476,7 @@
       <c r="I6" s="12"/>
       <c r="J6" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B6+C6+D6+E6+F6)/3+G6/3+H6/3+I6,0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1512,7 +1520,9 @@
       <c r="E8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="G8" s="12" t="n">
         <v>9</v>
       </c>
@@ -1520,7 +1530,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1539,7 +1549,9 @@
       <c r="E9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="13"/>
+      <c r="F9" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="G9" s="13" t="n">
         <v>6</v>
       </c>
@@ -1547,7 +1559,7 @@
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1564,7 +1576,9 @@
       <c r="E10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="12"/>
+      <c r="F10" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="G10" s="12" t="n">
         <v>7</v>
       </c>
@@ -1610,7 +1624,9 @@
       <c r="E12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="13"/>
+      <c r="F12" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="G12" s="13" t="n">
         <v>7</v>
       </c>
@@ -1618,7 +1634,7 @@
       <c r="I12" s="13"/>
       <c r="J12" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1633,7 +1649,9 @@
       <c r="E13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="12"/>
+      <c r="F13" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="G13" s="12" t="n">
         <v>6</v>
       </c>
@@ -1660,7 +1678,9 @@
       <c r="E14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="13"/>
+      <c r="F14" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="G14" s="13" t="n">
         <v>8</v>
       </c>
@@ -1702,8 +1722,12 @@
       <c r="C16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
+      <c r="D16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="F16" s="13"/>
       <c r="G16" s="13" t="n">
         <v>6</v>
@@ -1712,7 +1736,7 @@
       <c r="I16" s="13"/>
       <c r="J16" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B16+C16+D16+E16+F16)/3+G16/3+H16/3+I16,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1391,11 +1391,13 @@
       <c r="G3" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="13"/>
+      <c r="H3" s="13" t="n">
+        <v>8</v>
+      </c>
       <c r="I3" s="13"/>
       <c r="J3" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1420,11 +1422,13 @@
       <c r="G4" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="12"/>
+      <c r="H4" s="12" t="n">
+        <v>4</v>
+      </c>
       <c r="I4" s="12"/>
       <c r="J4" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1437,17 +1441,23 @@
       <c r="C5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="D5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="F5" s="13"/>
       <c r="G5" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="13"/>
+      <c r="H5" s="13" t="n">
+        <v>7</v>
+      </c>
       <c r="I5" s="13"/>
       <c r="J5" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B5+C5+D5+E5+F5)/3+G5/3+H5/3+I5,0))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1472,11 +1482,13 @@
       <c r="G6" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12" t="n">
+        <v>7</v>
+      </c>
       <c r="I6" s="12"/>
       <c r="J6" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B6+C6+D6+E6+F6)/3+G6/3+H6/3+I6,0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1495,15 +1507,19 @@
       <c r="E7" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="G7" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="12" t="n">
+        <v>7</v>
+      </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1526,11 +1542,13 @@
       <c r="G8" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12" t="n">
+        <v>3</v>
+      </c>
       <c r="I8" s="12"/>
       <c r="J8" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1555,11 +1573,13 @@
       <c r="G9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="13"/>
+      <c r="H9" s="13" t="n">
+        <v>10</v>
+      </c>
       <c r="I9" s="13"/>
       <c r="J9" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1582,11 +1602,13 @@
       <c r="G10" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="12" t="n">
+        <v>3</v>
+      </c>
       <c r="I10" s="12"/>
       <c r="J10" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1630,11 +1652,13 @@
       <c r="G12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="13"/>
+      <c r="H12" s="13" t="n">
+        <v>6</v>
+      </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1655,11 +1679,13 @@
       <c r="G13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="12"/>
+      <c r="H13" s="12" t="n">
+        <v>7</v>
+      </c>
       <c r="I13" s="12"/>
       <c r="J13" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B13+C13+D13+E13+F13)/3+G13/3+H13/3+I13,0))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1684,11 +1710,13 @@
       <c r="G14" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="13"/>
+      <c r="H14" s="13" t="n">
+        <v>7</v>
+      </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1705,11 +1733,13 @@
       <c r="G15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="12"/>
+      <c r="H15" s="12" t="n">
+        <v>4</v>
+      </c>
       <c r="I15" s="12"/>
       <c r="J15" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B15+C15+D15+E15+F15)/3+G15/3+H15/3+I15,0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1728,20 +1758,25 @@
       <c r="E16" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="G16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="13"/>
+      <c r="H16" s="13" t="n">
+        <v>7</v>
+      </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13" t="n">
         <f aca="false">MIN(10, ROUNDUP((B16+C16+D16+E16+F16)/3+G16/3+H16/3+I16,0))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K17" s="8"/>
     </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1,18 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tmp\FAKT_INFORMATICS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65055260-F1F2-41B1-BE1B-F468622B2942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="посещения" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="оценки" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="посещения" sheetId="1" r:id="rId1"/>
+    <sheet name="оценки" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,182 +37,179 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="56">
   <si>
-    <t xml:space="preserve">Column1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Алеев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Блинов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кирсанов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Коломоец</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кукушкин</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моисеев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Осипов</t>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Column6</t>
+  </si>
+  <si>
+    <t>Column7</t>
+  </si>
+  <si>
+    <t>Column8</t>
+  </si>
+  <si>
+    <t>Column9</t>
+  </si>
+  <si>
+    <t>Column10</t>
+  </si>
+  <si>
+    <t>Column11</t>
+  </si>
+  <si>
+    <t>Column12</t>
+  </si>
+  <si>
+    <t>Column13</t>
+  </si>
+  <si>
+    <t>Column14</t>
+  </si>
+  <si>
+    <t>Column15</t>
+  </si>
+  <si>
+    <t>Column16</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>2025-09-29</t>
+  </si>
+  <si>
+    <t>2025-10-06</t>
+  </si>
+  <si>
+    <t>2025-10-13</t>
+  </si>
+  <si>
+    <t>2025-10-20</t>
+  </si>
+  <si>
+    <t>2025-10-27</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>2025-11-17</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>Алеев</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Блинов</t>
+  </si>
+  <si>
+    <t>Кирсанов</t>
+  </si>
+  <si>
+    <t>Коломоец</t>
+  </si>
+  <si>
+    <t>Кукушкин</t>
+  </si>
+  <si>
+    <t>Моисеев</t>
+  </si>
+  <si>
+    <t>Осипов</t>
   </si>
   <si>
     <t xml:space="preserve">Погосян </t>
   </si>
   <si>
-    <t xml:space="preserve">Подкорытов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Титова</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фролова</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Хачоян</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цагадаев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чернейко</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КР1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КР2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">доп баллы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">итог</t>
+    <t>Подкорытов</t>
+  </si>
+  <si>
+    <t>Титова</t>
+  </si>
+  <si>
+    <t>Фролова</t>
+  </si>
+  <si>
+    <t>Хачоян</t>
+  </si>
+  <si>
+    <t>Цагадаев</t>
+  </si>
+  <si>
+    <t>Чернейко</t>
+  </si>
+  <si>
+    <t>лаба1</t>
+  </si>
+  <si>
+    <t>лаба2</t>
+  </si>
+  <si>
+    <t>лаба3</t>
+  </si>
+  <si>
+    <t>лаба4</t>
+  </si>
+  <si>
+    <t>лаба5</t>
+  </si>
+  <si>
+    <t>КР1</t>
+  </si>
+  <si>
+    <t>КР2</t>
+  </si>
+  <si>
+    <t>доп баллы</t>
+  </si>
+  <si>
+    <t>итог</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -207,22 +218,7 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -258,14 +254,14 @@
     </fill>
   </fills>
   <borders count="7">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFA9D18E"/>
       </left>
@@ -278,7 +274,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -289,7 +285,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FFA9D18E"/>
@@ -302,7 +298,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFA9D18E"/>
       </left>
@@ -313,7 +309,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -322,114 +318,49 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
-    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
+  <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Пояснение" xfId="1" builtinId="53" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -488,23 +419,331 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+  <a:themeElements>
+    <a:clrScheme name="Стандартная">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Стандартная">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Стандартная">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.7"/>
+    <col min="1" max="1025" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,7 +793,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>16</v>
@@ -602,7 +841,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -652,7 +891,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
@@ -702,7 +941,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -752,7 +991,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -762,7 +1001,7 @@
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -802,7 +1041,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -852,7 +1091,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -902,7 +1141,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -952,7 +1191,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
@@ -971,7 +1210,7 @@
       <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="5">
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -1002,7 +1241,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -1052,7 +1291,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1102,7 +1341,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1118,10 +1357,10 @@
       <c r="E13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="5">
         <v>1</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="5">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
@@ -1152,7 +1391,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -1202,7 +1441,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
@@ -1252,7 +1491,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -1303,31 +1542,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BE37"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="8.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="10" style="0" width="8.7"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="1025" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="10"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1339,7 +1570,7 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12" t="s">
         <v>47</v>
@@ -1369,249 +1600,251 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="13" t="n">
+      <c r="B3" s="13">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13">
+        <v>2</v>
+      </c>
+      <c r="D3" s="13">
+        <v>2</v>
+      </c>
+      <c r="E3" s="13">
+        <v>2</v>
+      </c>
+      <c r="F3" s="13">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13">
         <v>6</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="13">
         <v>8</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
+      <c r="J3" s="13">
+        <f t="shared" ref="J3:J16" si="0">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="12" t="n">
+      <c r="B4" s="12">
+        <v>2</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12">
+        <v>2</v>
+      </c>
+      <c r="E4" s="12">
+        <v>2</v>
+      </c>
+      <c r="F4" s="12">
+        <v>2</v>
+      </c>
+      <c r="G4" s="12">
         <v>8</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="12">
         <v>4</v>
       </c>
       <c r="I4" s="12"/>
-      <c r="J4" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
+      <c r="J4" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="13" t="n">
+      <c r="B5" s="13">
+        <v>2</v>
+      </c>
+      <c r="C5" s="13">
+        <v>2</v>
+      </c>
+      <c r="D5" s="13">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13">
         <v>2</v>
       </c>
       <c r="F5" s="13"/>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="13">
         <v>9</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="13">
         <v>7</v>
       </c>
       <c r="I5" s="13"/>
-      <c r="J5" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B5+C5+D5+E5+F5)/3+G5/3+H5/3+I5,0))</f>
+      <c r="J5" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="12" t="n">
+      <c r="B6" s="12">
+        <v>2</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2</v>
+      </c>
+      <c r="F6" s="12">
+        <v>2</v>
+      </c>
+      <c r="G6" s="12">
         <v>6</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="12">
         <v>7</v>
       </c>
       <c r="I6" s="12"/>
-      <c r="J6" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B6+C6+D6+E6+F6)/3+G6/3+H6/3+I6,0))</f>
+      <c r="J6" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="12" t="n">
+      <c r="B7" s="12">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12">
+        <v>2</v>
+      </c>
+      <c r="D7" s="12">
+        <v>2</v>
+      </c>
+      <c r="E7" s="12">
+        <v>2</v>
+      </c>
+      <c r="F7" s="12">
+        <v>2</v>
+      </c>
+      <c r="G7" s="12">
         <v>8</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="12">
         <v>7</v>
       </c>
       <c r="I7" s="12"/>
-      <c r="J7" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
+      <c r="J7" s="13">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="12" t="n">
+      <c r="D8" s="12">
+        <v>2</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12">
+        <v>2</v>
+      </c>
+      <c r="G8" s="12">
         <v>9</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="12">
         <v>3</v>
       </c>
       <c r="I8" s="12"/>
-      <c r="J8" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
+      <c r="J8" s="13">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="13" t="n">
+      <c r="B9" s="13">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13">
+        <v>2</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2</v>
+      </c>
+      <c r="E9" s="13">
+        <v>2</v>
+      </c>
+      <c r="F9" s="13">
+        <v>2</v>
+      </c>
+      <c r="G9" s="13">
         <v>6</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="13">
         <v>10</v>
       </c>
       <c r="I9" s="13"/>
-      <c r="J9" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
+      <c r="J9" s="13">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="12" t="n">
+      <c r="B10" s="12">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12">
+        <v>2</v>
+      </c>
+      <c r="D10" s="12">
+        <v>2</v>
+      </c>
+      <c r="E10" s="12">
+        <v>2</v>
+      </c>
+      <c r="F10" s="12">
+        <v>2</v>
+      </c>
+      <c r="G10" s="12">
         <v>7</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="12">
         <v>3</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J10" s="13">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -1620,171 +1853,170 @@
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="13">
         <v>10</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
-      <c r="J11" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B11+C11+D11+E11+F11)/3+G11/3+H11/3+I11,0))</f>
+      <c r="J11" s="13">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="13" t="n">
+      <c r="B12" s="13">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13">
+        <v>2</v>
+      </c>
+      <c r="D12" s="13">
+        <v>2</v>
+      </c>
+      <c r="E12" s="13">
+        <v>2</v>
+      </c>
+      <c r="F12" s="13">
+        <v>2</v>
+      </c>
+      <c r="G12" s="13">
         <v>7</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="13">
         <v>6</v>
       </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
+      <c r="J12" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="12" t="n">
+      <c r="D13" s="12">
+        <v>2</v>
+      </c>
+      <c r="E13" s="12">
+        <v>2</v>
+      </c>
+      <c r="F13" s="12">
+        <v>2</v>
+      </c>
+      <c r="G13" s="12">
         <v>6</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="12">
         <v>7</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B13+C13+D13+E13+F13)/3+G13/3+H13/3+I13,0))</f>
+      <c r="J13" s="13">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="13" t="n">
+      <c r="B14" s="13">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13">
+        <v>2</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13">
+        <v>2</v>
+      </c>
+      <c r="F14" s="13">
+        <v>2</v>
+      </c>
+      <c r="G14" s="13">
         <v>8</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="13">
         <v>7</v>
       </c>
       <c r="I14" s="13"/>
-      <c r="J14" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
+      <c r="J14" s="13">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="12">
         <v>2</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="12">
         <v>9</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="12">
         <v>4</v>
       </c>
       <c r="I15" s="12"/>
-      <c r="J15" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B15+C15+D15+E15+F15)/3+G15/3+H15/3+I15,0))</f>
+      <c r="J15" s="13">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="13" t="n">
+      <c r="B16" s="13">
+        <v>2</v>
+      </c>
+      <c r="C16" s="13">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2</v>
+      </c>
+      <c r="E16" s="13">
+        <v>2</v>
+      </c>
+      <c r="F16" s="13">
+        <v>2</v>
+      </c>
+      <c r="G16" s="13">
         <v>6</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="13">
         <v>7</v>
       </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B16+C16+D16+E16+F16)/3+G16/3+H16/3+I16,0))</f>
+      <c r="J16" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
       <c r="K17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="E26" s="14"/>
@@ -1838,14 +2070,14 @@
       <c r="BA26" s="14"/>
       <c r="BB26" s="14"/>
       <c r="BC26" s="14"/>
-      <c r="BD26" s="14" t="n">
+      <c r="BD26" s="14">
         <v>18</v>
       </c>
-      <c r="BE26" s="14" t="n">
+      <c r="BE26" s="14">
         <v>11</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="E27" s="14"/>
@@ -1899,14 +2131,14 @@
       <c r="BA27" s="14"/>
       <c r="BB27" s="14"/>
       <c r="BC27" s="14"/>
-      <c r="BD27" s="14" t="n">
+      <c r="BD27" s="14">
         <v>11</v>
       </c>
-      <c r="BE27" s="14" t="n">
+      <c r="BE27" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="E28" s="14"/>
@@ -1960,14 +2192,14 @@
       <c r="BA28" s="14"/>
       <c r="BB28" s="14"/>
       <c r="BC28" s="14"/>
-      <c r="BD28" s="14" t="n">
+      <c r="BD28" s="14">
         <v>0</v>
       </c>
-      <c r="BE28" s="14" t="n">
+      <c r="BE28" s="14">
         <v>54</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="E29" s="14"/>
@@ -2021,14 +2253,14 @@
       <c r="BA29" s="14"/>
       <c r="BB29" s="14"/>
       <c r="BC29" s="14"/>
-      <c r="BD29" s="14" t="n">
+      <c r="BD29" s="14">
         <v>8</v>
       </c>
-      <c r="BE29" s="14" t="n">
+      <c r="BE29" s="14">
         <v>31</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="E30" s="14"/>
@@ -2082,14 +2314,14 @@
       <c r="BA30" s="14"/>
       <c r="BB30" s="14"/>
       <c r="BC30" s="14"/>
-      <c r="BD30" s="14" t="n">
+      <c r="BD30" s="14">
         <v>21</v>
       </c>
-      <c r="BE30" s="14" t="n">
+      <c r="BE30" s="14">
         <v>36</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="E31" s="14"/>
@@ -2143,14 +2375,14 @@
       <c r="BA31" s="14"/>
       <c r="BB31" s="14"/>
       <c r="BC31" s="14"/>
-      <c r="BD31" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE31" s="14" t="n">
+      <c r="BD31" s="14">
+        <v>2</v>
+      </c>
+      <c r="BE31" s="14">
         <v>17</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="E32" s="14"/>
@@ -2204,14 +2436,14 @@
       <c r="BA32" s="14"/>
       <c r="BB32" s="14"/>
       <c r="BC32" s="14"/>
-      <c r="BD32" s="14" t="n">
+      <c r="BD32" s="14">
         <v>0</v>
       </c>
-      <c r="BE32" s="14" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BE32" s="14">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="E33" s="14"/>
@@ -2265,14 +2497,14 @@
       <c r="BA33" s="14"/>
       <c r="BB33" s="14"/>
       <c r="BC33" s="14"/>
-      <c r="BD33" s="14" t="n">
+      <c r="BD33" s="14">
         <v>23</v>
       </c>
-      <c r="BE33" s="14" t="n">
+      <c r="BE33" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="E34" s="14"/>
@@ -2326,14 +2558,14 @@
       <c r="BA34" s="14"/>
       <c r="BB34" s="14"/>
       <c r="BC34" s="14"/>
-      <c r="BD34" s="14" t="n">
+      <c r="BD34" s="14">
         <v>18</v>
       </c>
-      <c r="BE34" s="14" t="n">
+      <c r="BE34" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="E35" s="14"/>
@@ -2387,14 +2619,14 @@
       <c r="BA35" s="14"/>
       <c r="BB35" s="14"/>
       <c r="BC35" s="14"/>
-      <c r="BD35" s="14" t="n">
+      <c r="BD35" s="14">
         <v>17</v>
       </c>
-      <c r="BE35" s="14" t="n">
+      <c r="BE35" s="14">
         <v>14</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="E36" s="14"/>
@@ -2448,14 +2680,14 @@
       <c r="BA36" s="14"/>
       <c r="BB36" s="14"/>
       <c r="BC36" s="14"/>
-      <c r="BD36" s="14" t="n">
+      <c r="BD36" s="14">
         <v>17</v>
       </c>
-      <c r="BE36" s="14" t="n">
+      <c r="BE36" s="14">
         <v>46</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="E37" s="14"/>
@@ -2509,20 +2741,15 @@
       <c r="BA37" s="14"/>
       <c r="BB37" s="14"/>
       <c r="BC37" s="14"/>
-      <c r="BD37" s="14" t="n">
+      <c r="BD37" s="14">
         <v>18</v>
       </c>
-      <c r="BE37" s="14" t="n">
+      <c r="BE37" s="14">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/marks.xlsx
+++ b/marks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tmp\FAKT_INFORMATICS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65055260-F1F2-41B1-BE1B-F468622B2942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4091BA0-2AB0-4251-AA15-407346B8A31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1678,7 +1678,9 @@
       <c r="E5" s="13">
         <v>2</v>
       </c>
-      <c r="F5" s="13"/>
+      <c r="F5" s="13">
+        <v>2</v>
+      </c>
       <c r="G5" s="13">
         <v>9</v>
       </c>
@@ -1688,7 +1690,7 @@
       <c r="I5" s="13"/>
       <c r="J5" s="13">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1,32 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tmp\FAKT_INFORMATICS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4091BA0-2AB0-4251-AA15-407346B8A31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="посещения" sheetId="1" r:id="rId1"/>
-    <sheet name="оценки" sheetId="2" r:id="rId2"/>
+    <sheet name="посещения" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="оценки" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="оценки 2 семестр" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -35,181 +22,196 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="56">
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
-  </si>
-  <si>
-    <t>Column4</t>
-  </si>
-  <si>
-    <t>Column5</t>
-  </si>
-  <si>
-    <t>Column6</t>
-  </si>
-  <si>
-    <t>Column7</t>
-  </si>
-  <si>
-    <t>Column8</t>
-  </si>
-  <si>
-    <t>Column9</t>
-  </si>
-  <si>
-    <t>Column10</t>
-  </si>
-  <si>
-    <t>Column11</t>
-  </si>
-  <si>
-    <t>Column12</t>
-  </si>
-  <si>
-    <t>Column13</t>
-  </si>
-  <si>
-    <t>Column14</t>
-  </si>
-  <si>
-    <t>Column15</t>
-  </si>
-  <si>
-    <t>Column16</t>
-  </si>
-  <si>
-    <t>2025-09-01</t>
-  </si>
-  <si>
-    <t>2025-09-08</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>2025-09-29</t>
-  </si>
-  <si>
-    <t>2025-10-06</t>
-  </si>
-  <si>
-    <t>2025-10-13</t>
-  </si>
-  <si>
-    <t>2025-10-20</t>
-  </si>
-  <si>
-    <t>2025-10-27</t>
-  </si>
-  <si>
-    <t>2025-11-03</t>
-  </si>
-  <si>
-    <t>2025-11-10</t>
-  </si>
-  <si>
-    <t>2025-11-17</t>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>Алеев</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Блинов</t>
-  </si>
-  <si>
-    <t>Кирсанов</t>
-  </si>
-  <si>
-    <t>Коломоец</t>
-  </si>
-  <si>
-    <t>Кукушкин</t>
-  </si>
-  <si>
-    <t>Моисеев</t>
-  </si>
-  <si>
-    <t>Осипов</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="60">
+  <si>
+    <t xml:space="preserve">Column1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Алеев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Блинов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кирсанов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коломоец</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кукушкин</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моисеев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Осипов</t>
   </si>
   <si>
     <t xml:space="preserve">Погосян </t>
   </si>
   <si>
-    <t>Подкорытов</t>
-  </si>
-  <si>
-    <t>Титова</t>
-  </si>
-  <si>
-    <t>Фролова</t>
-  </si>
-  <si>
-    <t>Хачоян</t>
-  </si>
-  <si>
-    <t>Цагадаев</t>
-  </si>
-  <si>
-    <t>Чернейко</t>
-  </si>
-  <si>
-    <t>лаба1</t>
-  </si>
-  <si>
-    <t>лаба2</t>
-  </si>
-  <si>
-    <t>лаба3</t>
-  </si>
-  <si>
-    <t>лаба4</t>
-  </si>
-  <si>
-    <t>лаба5</t>
-  </si>
-  <si>
-    <t>КР1</t>
-  </si>
-  <si>
-    <t>КР2</t>
-  </si>
-  <si>
-    <t>доп баллы</t>
-  </si>
-  <si>
-    <t>итог</t>
+    <t xml:space="preserve">Подкорытов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Титова</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фролова</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Хачоян</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цагадаев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чернейко</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КР1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КР2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">доп баллы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">итог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кр / хакатон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">проект</t>
+  </si>
+  <si>
+    <t xml:space="preserve">теор. Зачёт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Итог</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -218,7 +220,22 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -254,14 +271,14 @@
     </fill>
   </fills>
   <borders count="7">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFA9D18E"/>
       </left>
@@ -274,7 +291,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top style="thin">
@@ -285,7 +302,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FFA9D18E"/>
@@ -298,7 +315,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFA9D18E"/>
       </left>
@@ -309,7 +326,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top style="thin">
@@ -318,49 +335,114 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Пояснение" xfId="1" builtinId="53" customBuiltin="1"/>
+  <cellStyles count="7">
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -419,331 +501,23 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
-  <a:themeElements>
-    <a:clrScheme name="Стандартная">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4472C4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Стандартная">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1025" width="8.7109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,7 +567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>16</v>
@@ -841,7 +615,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -891,7 +665,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
@@ -941,7 +715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -991,7 +765,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -1001,7 +775,7 @@
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -1041,7 +815,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -1091,7 +865,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -1141,7 +915,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -1191,7 +965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
@@ -1210,7 +984,7 @@
       <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -1241,7 +1015,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -1291,7 +1065,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1341,7 +1115,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1357,10 +1131,10 @@
       <c r="E13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
@@ -1391,7 +1165,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -1441,7 +1215,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
@@ -1491,7 +1265,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -1542,23 +1316,31 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:BE37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="1025" width="8.7109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="10" style="0" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1570,7 +1352,7 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12"/>
       <c r="B2" s="12" t="s">
         <v>47</v>
@@ -1600,253 +1382,253 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="13">
-        <v>2</v>
-      </c>
-      <c r="C3" s="13">
-        <v>2</v>
-      </c>
-      <c r="D3" s="13">
-        <v>2</v>
-      </c>
-      <c r="E3" s="13">
-        <v>2</v>
-      </c>
-      <c r="F3" s="13">
-        <v>2</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="B3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="13" t="n">
         <v>8</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="13">
-        <f t="shared" ref="J3:J16" si="0">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
+      <c r="J3" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="12">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12">
-        <v>2</v>
-      </c>
-      <c r="E4" s="12">
-        <v>2</v>
-      </c>
-      <c r="F4" s="12">
-        <v>2</v>
-      </c>
-      <c r="G4" s="12">
+      <c r="B4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I4" s="12"/>
-      <c r="J4" s="13">
-        <f t="shared" si="0"/>
+      <c r="J4" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="13">
-        <v>2</v>
-      </c>
-      <c r="C5" s="13">
-        <v>2</v>
-      </c>
-      <c r="D5" s="13">
-        <v>2</v>
-      </c>
-      <c r="E5" s="13">
-        <v>2</v>
-      </c>
-      <c r="F5" s="13">
-        <v>2</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="B5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="13" t="n">
         <v>7</v>
       </c>
       <c r="I5" s="13"/>
-      <c r="J5" s="13">
-        <f t="shared" si="0"/>
+      <c r="J5" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B5+C5+D5+E5+F5)/3+G5/3+H5/3+I5,0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="12">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12">
-        <v>2</v>
-      </c>
-      <c r="E6" s="12">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12">
-        <v>2</v>
-      </c>
-      <c r="G6" s="12">
+      <c r="B6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I6" s="12"/>
-      <c r="J6" s="13">
-        <f t="shared" si="0"/>
+      <c r="J6" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B6+C6+D6+E6+F6)/3+G6/3+H6/3+I6,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="12">
-        <v>2</v>
-      </c>
-      <c r="C7" s="12">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12">
-        <v>2</v>
-      </c>
-      <c r="E7" s="12">
-        <v>2</v>
-      </c>
-      <c r="F7" s="12">
-        <v>2</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="B7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I7" s="12"/>
-      <c r="J7" s="13">
-        <f t="shared" si="0"/>
+      <c r="J7" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="12">
-        <v>2</v>
-      </c>
-      <c r="E8" s="12">
-        <v>2</v>
-      </c>
-      <c r="F8" s="12">
-        <v>2</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="D8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="12"/>
-      <c r="J8" s="13">
-        <f t="shared" si="0"/>
+      <c r="J8" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="13">
-        <v>2</v>
-      </c>
-      <c r="C9" s="13">
-        <v>2</v>
-      </c>
-      <c r="D9" s="13">
-        <v>2</v>
-      </c>
-      <c r="E9" s="13">
-        <v>2</v>
-      </c>
-      <c r="F9" s="13">
-        <v>2</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="B9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="13" t="n">
         <v>10</v>
       </c>
       <c r="I9" s="13"/>
-      <c r="J9" s="13">
-        <f t="shared" si="0"/>
+      <c r="J9" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12">
-        <v>2</v>
-      </c>
-      <c r="C10" s="12">
-        <v>2</v>
-      </c>
-      <c r="D10" s="12">
-        <v>2</v>
-      </c>
-      <c r="E10" s="12">
-        <v>2</v>
-      </c>
-      <c r="F10" s="12">
-        <v>2</v>
-      </c>
-      <c r="G10" s="12">
+      <c r="B10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="13">
-        <f t="shared" si="0"/>
+      <c r="J10" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -1855,170 +1637,170 @@
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="13">
+      <c r="G11" s="13" t="n">
         <v>10</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
-      <c r="J11" s="13">
-        <f t="shared" si="0"/>
+      <c r="J11" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B11+C11+D11+E11+F11)/3+G11/3+H11/3+I11,0))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="13">
-        <v>2</v>
-      </c>
-      <c r="C12" s="13">
-        <v>2</v>
-      </c>
-      <c r="D12" s="13">
-        <v>2</v>
-      </c>
-      <c r="E12" s="13">
-        <v>2</v>
-      </c>
-      <c r="F12" s="13">
-        <v>2</v>
-      </c>
-      <c r="G12" s="13">
+      <c r="B12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="13" t="n">
         <v>6</v>
       </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="13">
-        <f t="shared" si="0"/>
+      <c r="J12" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="12">
-        <v>2</v>
-      </c>
-      <c r="E13" s="12">
-        <v>2</v>
-      </c>
-      <c r="F13" s="12">
-        <v>2</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="D13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="13">
-        <f t="shared" si="0"/>
+      <c r="J13" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B13+C13+D13+E13+F13)/3+G13/3+H13/3+I13,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="13">
-        <v>2</v>
-      </c>
-      <c r="C14" s="13">
-        <v>2</v>
-      </c>
-      <c r="D14" s="13">
-        <v>2</v>
-      </c>
-      <c r="E14" s="13">
-        <v>2</v>
-      </c>
-      <c r="F14" s="13">
-        <v>2</v>
-      </c>
-      <c r="G14" s="13">
+      <c r="B14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="13" t="n">
         <v>7</v>
       </c>
       <c r="I14" s="13"/>
-      <c r="J14" s="13">
-        <f t="shared" si="0"/>
+      <c r="J14" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="12">
+      <c r="C15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="12">
+      <c r="G15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I15" s="12"/>
-      <c r="J15" s="13">
-        <f t="shared" si="0"/>
+      <c r="J15" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B15+C15+D15+E15+F15)/3+G15/3+H15/3+I15,0))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="13">
-        <v>2</v>
-      </c>
-      <c r="C16" s="13">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13">
-        <v>2</v>
-      </c>
-      <c r="E16" s="13">
-        <v>2</v>
-      </c>
-      <c r="F16" s="13">
-        <v>2</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="B16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="13" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="13">
-        <f t="shared" si="0"/>
+      <c r="J16" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B16+C16+D16+E16+F16)/3+G16/3+H16/3+I16,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K17" s="8"/>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="E26" s="14"/>
@@ -2072,14 +1854,14 @@
       <c r="BA26" s="14"/>
       <c r="BB26" s="14"/>
       <c r="BC26" s="14"/>
-      <c r="BD26" s="14">
+      <c r="BD26" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE26" s="14">
+      <c r="BE26" s="14" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="E27" s="14"/>
@@ -2133,14 +1915,14 @@
       <c r="BA27" s="14"/>
       <c r="BB27" s="14"/>
       <c r="BC27" s="14"/>
-      <c r="BD27" s="14">
+      <c r="BD27" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="BE27" s="14">
+      <c r="BE27" s="14" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="E28" s="14"/>
@@ -2194,14 +1976,14 @@
       <c r="BA28" s="14"/>
       <c r="BB28" s="14"/>
       <c r="BC28" s="14"/>
-      <c r="BD28" s="14">
+      <c r="BD28" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BE28" s="14">
+      <c r="BE28" s="14" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="E29" s="14"/>
@@ -2255,14 +2037,14 @@
       <c r="BA29" s="14"/>
       <c r="BB29" s="14"/>
       <c r="BC29" s="14"/>
-      <c r="BD29" s="14">
+      <c r="BD29" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="BE29" s="14">
+      <c r="BE29" s="14" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="E30" s="14"/>
@@ -2316,14 +2098,14 @@
       <c r="BA30" s="14"/>
       <c r="BB30" s="14"/>
       <c r="BC30" s="14"/>
-      <c r="BD30" s="14">
+      <c r="BD30" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="BE30" s="14">
+      <c r="BE30" s="14" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="E31" s="14"/>
@@ -2377,14 +2159,14 @@
       <c r="BA31" s="14"/>
       <c r="BB31" s="14"/>
       <c r="BC31" s="14"/>
-      <c r="BD31" s="14">
-        <v>2</v>
-      </c>
-      <c r="BE31" s="14">
+      <c r="BD31" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE31" s="14" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="E32" s="14"/>
@@ -2438,14 +2220,14 @@
       <c r="BA32" s="14"/>
       <c r="BB32" s="14"/>
       <c r="BC32" s="14"/>
-      <c r="BD32" s="14">
+      <c r="BD32" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BE32" s="14">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BE32" s="14" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="E33" s="14"/>
@@ -2499,14 +2281,14 @@
       <c r="BA33" s="14"/>
       <c r="BB33" s="14"/>
       <c r="BC33" s="14"/>
-      <c r="BD33" s="14">
+      <c r="BD33" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="BE33" s="14">
+      <c r="BE33" s="14" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="E34" s="14"/>
@@ -2560,14 +2342,14 @@
       <c r="BA34" s="14"/>
       <c r="BB34" s="14"/>
       <c r="BC34" s="14"/>
-      <c r="BD34" s="14">
+      <c r="BD34" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE34" s="14">
+      <c r="BE34" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="E35" s="14"/>
@@ -2621,14 +2403,14 @@
       <c r="BA35" s="14"/>
       <c r="BB35" s="14"/>
       <c r="BC35" s="14"/>
-      <c r="BD35" s="14">
+      <c r="BD35" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="BE35" s="14">
+      <c r="BE35" s="14" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="E36" s="14"/>
@@ -2682,14 +2464,14 @@
       <c r="BA36" s="14"/>
       <c r="BB36" s="14"/>
       <c r="BC36" s="14"/>
-      <c r="BD36" s="14">
+      <c r="BD36" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="BE36" s="14">
+      <c r="BE36" s="14" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="E37" s="14"/>
@@ -2743,15 +2525,248 @@
       <c r="BA37" s="14"/>
       <c r="BB37" s="14"/>
       <c r="BC37" s="14"/>
-      <c r="BD37" s="14">
+      <c r="BD37" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE37" s="14">
+      <c r="BE37" s="14" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="12" t="n">
+        <f aca="false">MIN(ROUND((B3+C3+D3) / 3,0), 10)</f>
+        <v>3</v>
+      </c>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12" t="n">
+        <f aca="false">MIN(ROUND((B4+C4+D4) / 3,0), 10)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="12" t="n">
+        <f aca="false">MIN(ROUND((C5+D5) / 2,0), 10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12" t="n">
+        <f aca="false">MIN(ROUND((B6+C6+D6) / 3,0), 10)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12" t="n">
+        <f aca="false">MIN(ROUND((B7+C7+D7) / 3,0), 10)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="n">
+        <f aca="false">MIN(ROUND((B8+C8+D8) / 3,0), 10)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="12" t="n">
+        <f aca="false">MIN(ROUND((B9+C9+D9) / 3,0), 10)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="n">
+        <f aca="false">MIN(ROUND((B10+C10+D10) / 3,0), 10)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="12" t="n">
+        <f aca="false">MIN(ROUND((B11+C11+D11) / 3,0), 10)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="n">
+        <f aca="false">MIN(ROUND((B12+C12+D12) / 3,0), 10)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="12" t="n">
+        <f aca="false">MIN(ROUND((B13+C13+D13) / 3,0), 10)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12" t="n">
+        <f aca="false">MIN(ROUND((B14+C14+D14) / 3,0), 10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="12" t="n">
+        <f aca="false">MIN(ROUND((B15+C15+D15) / 3,0), 10)</f>
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/marks.xlsx
+++ b/marks.xlsx
@@ -2587,10 +2587,12 @@
         <v>9</v>
       </c>
       <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
+      <c r="D3" s="13" t="n">
+        <v>9</v>
+      </c>
       <c r="E3" s="12" t="n">
         <f aca="false">MIN(ROUND((B3+C3+D3) / 3,0), 10)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J3" s="13"/>
     </row>
@@ -2628,10 +2630,12 @@
         <v>10</v>
       </c>
       <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="D6" s="12" t="n">
+        <v>9</v>
+      </c>
       <c r="E6" s="12" t="n">
         <f aca="false">MIN(ROUND((B6+C6+D6) / 3,0), 10)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2656,10 +2660,12 @@
         <v>10</v>
       </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="D8" s="12" t="n">
+        <v>7</v>
+      </c>
       <c r="E8" s="12" t="n">
         <f aca="false">MIN(ROUND((B8+C8+D8) / 3,0), 10)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2670,10 +2676,12 @@
         <v>8</v>
       </c>
       <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="D9" s="13" t="n">
+        <v>9</v>
+      </c>
       <c r="E9" s="12" t="n">
         <f aca="false">MIN(ROUND((B9+C9+D9) / 3,0), 10)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2698,10 +2706,12 @@
         <v>8</v>
       </c>
       <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
+      <c r="D11" s="13" t="n">
+        <v>9</v>
+      </c>
       <c r="E11" s="12" t="n">
         <f aca="false">MIN(ROUND((B11+C11+D11) / 3,0), 10)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2726,10 +2736,12 @@
         <v>8</v>
       </c>
       <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
+      <c r="D13" s="13" t="n">
+        <v>9</v>
+      </c>
       <c r="E13" s="12" t="n">
         <f aca="false">MIN(ROUND((B13+C13+D13) / 3,0), 10)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1,19 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tutoring\FAKT_INFORMATICS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902C6767-0F6C-4C78-BA0A-0AF906E1098F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="посещения" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="оценки" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="оценки 2 семестр" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="посещения" sheetId="1" r:id="rId1"/>
+    <sheet name="оценки" sheetId="2" r:id="rId2"/>
+    <sheet name="оценки 2 семестр" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,196 +36,220 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="60">
-  <si>
-    <t xml:space="preserve">Column1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Алеев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Блинов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кирсанов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Коломоец</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кукушкин</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моисеев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Осипов</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="69">
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Column6</t>
+  </si>
+  <si>
+    <t>Column7</t>
+  </si>
+  <si>
+    <t>Column8</t>
+  </si>
+  <si>
+    <t>Column9</t>
+  </si>
+  <si>
+    <t>Column10</t>
+  </si>
+  <si>
+    <t>Column11</t>
+  </si>
+  <si>
+    <t>Column12</t>
+  </si>
+  <si>
+    <t>Column13</t>
+  </si>
+  <si>
+    <t>Column14</t>
+  </si>
+  <si>
+    <t>Column15</t>
+  </si>
+  <si>
+    <t>Column16</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>2025-09-29</t>
+  </si>
+  <si>
+    <t>2025-10-06</t>
+  </si>
+  <si>
+    <t>2025-10-13</t>
+  </si>
+  <si>
+    <t>2025-10-20</t>
+  </si>
+  <si>
+    <t>2025-10-27</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>2025-11-17</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>Алеев</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Блинов</t>
+  </si>
+  <si>
+    <t>Кирсанов</t>
+  </si>
+  <si>
+    <t>Коломоец</t>
+  </si>
+  <si>
+    <t>Кукушкин</t>
+  </si>
+  <si>
+    <t>Моисеев</t>
+  </si>
+  <si>
+    <t>Осипов</t>
   </si>
   <si>
     <t xml:space="preserve">Погосян </t>
   </si>
   <si>
-    <t xml:space="preserve">Подкорытов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Титова</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фролова</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Хачоян</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цагадаев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чернейко</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">лаба5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КР1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КР2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">доп баллы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">итог</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кр / хакатон</t>
-  </si>
-  <si>
-    <t xml:space="preserve">проект</t>
-  </si>
-  <si>
-    <t xml:space="preserve">теор. Зачёт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Итог</t>
+    <t>Подкорытов</t>
+  </si>
+  <si>
+    <t>Титова</t>
+  </si>
+  <si>
+    <t>Фролова</t>
+  </si>
+  <si>
+    <t>Хачоян</t>
+  </si>
+  <si>
+    <t>Цагадаев</t>
+  </si>
+  <si>
+    <t>Чернейко</t>
+  </si>
+  <si>
+    <t>лаба1</t>
+  </si>
+  <si>
+    <t>лаба2</t>
+  </si>
+  <si>
+    <t>лаба3</t>
+  </si>
+  <si>
+    <t>лаба4</t>
+  </si>
+  <si>
+    <t>лаба5</t>
+  </si>
+  <si>
+    <t>КР1</t>
+  </si>
+  <si>
+    <t>КР2</t>
+  </si>
+  <si>
+    <t>доп баллы</t>
+  </si>
+  <si>
+    <t>итог</t>
+  </si>
+  <si>
+    <t>Кр / хакатон</t>
+  </si>
+  <si>
+    <t>проект</t>
+  </si>
+  <si>
+    <t>теор. Зачёт</t>
+  </si>
+  <si>
+    <t>Итог</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>fixes</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>Lunar Base Simulator</t>
+  </si>
+  <si>
+    <t>Strategy Game</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Морской бой</t>
+  </si>
+  <si>
+    <t>бот для бронирования</t>
+  </si>
+  <si>
+    <t>лифт</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -220,22 +258,7 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -250,7 +273,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,16 +292,52 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFA9D18E"/>
       </left>
@@ -291,7 +350,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -302,7 +361,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FFA9D18E"/>
@@ -315,7 +374,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFA9D18E"/>
       </left>
@@ -326,7 +385,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -335,114 +394,56 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
-    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
+  <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Пояснение" xfId="1" builtinId="53" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -501,23 +502,331 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+  <a:themeElements>
+    <a:clrScheme name="Стандартная">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Стандартная">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Стандартная">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.71"/>
+    <col min="1" max="1025" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>16</v>
@@ -615,7 +924,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -665,7 +974,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
@@ -715,7 +1024,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -765,7 +1074,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -775,7 +1084,7 @@
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -815,7 +1124,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -865,7 +1174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -915,7 +1224,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -965,7 +1274,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
@@ -984,7 +1293,7 @@
       <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="5">
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -1015,7 +1324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -1065,7 +1374,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1115,7 +1424,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1131,10 +1440,10 @@
       <c r="E13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="5">
         <v>1</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="5">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
@@ -1165,7 +1474,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -1215,7 +1524,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
@@ -1265,7 +1574,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -1316,31 +1625,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BE37"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="10" style="0" width="8.71"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="1025" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="10"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1352,7 +1653,7 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12" t="s">
         <v>47</v>
@@ -1382,253 +1683,253 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="13" t="n">
+      <c r="B3" s="13">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13">
+        <v>2</v>
+      </c>
+      <c r="D3" s="13">
+        <v>2</v>
+      </c>
+      <c r="E3" s="13">
+        <v>2</v>
+      </c>
+      <c r="F3" s="13">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13">
         <v>6</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="13">
         <v>8</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
+      <c r="J3" s="13">
+        <f t="shared" ref="J3:J16" si="0">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="12" t="n">
+      <c r="B4" s="12">
+        <v>2</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12">
+        <v>2</v>
+      </c>
+      <c r="E4" s="12">
+        <v>2</v>
+      </c>
+      <c r="F4" s="12">
+        <v>2</v>
+      </c>
+      <c r="G4" s="12">
         <v>8</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="12">
         <v>4</v>
       </c>
       <c r="I4" s="12"/>
-      <c r="J4" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
+      <c r="J4" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="13" t="n">
+      <c r="B5" s="13">
+        <v>2</v>
+      </c>
+      <c r="C5" s="13">
+        <v>2</v>
+      </c>
+      <c r="D5" s="13">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13">
+        <v>2</v>
+      </c>
+      <c r="F5" s="13">
+        <v>2</v>
+      </c>
+      <c r="G5" s="13">
         <v>9</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="13">
         <v>7</v>
       </c>
       <c r="I5" s="13"/>
-      <c r="J5" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B5+C5+D5+E5+F5)/3+G5/3+H5/3+I5,0))</f>
+      <c r="J5" s="13">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="12" t="n">
+      <c r="B6" s="12">
+        <v>2</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2</v>
+      </c>
+      <c r="F6" s="12">
+        <v>2</v>
+      </c>
+      <c r="G6" s="12">
         <v>6</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="12">
         <v>7</v>
       </c>
       <c r="I6" s="12"/>
-      <c r="J6" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B6+C6+D6+E6+F6)/3+G6/3+H6/3+I6,0))</f>
+      <c r="J6" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="12" t="n">
+      <c r="B7" s="12">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12">
+        <v>2</v>
+      </c>
+      <c r="D7" s="12">
+        <v>2</v>
+      </c>
+      <c r="E7" s="12">
+        <v>2</v>
+      </c>
+      <c r="F7" s="12">
+        <v>2</v>
+      </c>
+      <c r="G7" s="12">
         <v>8</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="12">
         <v>7</v>
       </c>
       <c r="I7" s="12"/>
-      <c r="J7" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
+      <c r="J7" s="13">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="12" t="n">
+      <c r="D8" s="12">
+        <v>2</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12">
+        <v>2</v>
+      </c>
+      <c r="G8" s="12">
         <v>9</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="12">
         <v>3</v>
       </c>
       <c r="I8" s="12"/>
-      <c r="J8" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
+      <c r="J8" s="13">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="13" t="n">
+      <c r="B9" s="13">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13">
+        <v>2</v>
+      </c>
+      <c r="D9" s="13">
+        <v>2</v>
+      </c>
+      <c r="E9" s="13">
+        <v>2</v>
+      </c>
+      <c r="F9" s="13">
+        <v>2</v>
+      </c>
+      <c r="G9" s="13">
         <v>6</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="13">
         <v>10</v>
       </c>
       <c r="I9" s="13"/>
-      <c r="J9" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
+      <c r="J9" s="13">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="12" t="n">
+      <c r="B10" s="12">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12">
+        <v>2</v>
+      </c>
+      <c r="D10" s="12">
+        <v>2</v>
+      </c>
+      <c r="E10" s="12">
+        <v>2</v>
+      </c>
+      <c r="F10" s="12">
+        <v>2</v>
+      </c>
+      <c r="G10" s="12">
         <v>7</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="12">
         <v>3</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
+      <c r="J10" s="13">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -1637,170 +1938,170 @@
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="13">
         <v>10</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
-      <c r="J11" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B11+C11+D11+E11+F11)/3+G11/3+H11/3+I11,0))</f>
+      <c r="J11" s="13">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="13" t="n">
+      <c r="B12" s="13">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13">
+        <v>2</v>
+      </c>
+      <c r="D12" s="13">
+        <v>2</v>
+      </c>
+      <c r="E12" s="13">
+        <v>2</v>
+      </c>
+      <c r="F12" s="13">
+        <v>2</v>
+      </c>
+      <c r="G12" s="13">
         <v>7</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="13">
         <v>6</v>
       </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
+      <c r="J12" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="12" t="n">
+      <c r="D13" s="12">
+        <v>2</v>
+      </c>
+      <c r="E13" s="12">
+        <v>2</v>
+      </c>
+      <c r="F13" s="12">
+        <v>2</v>
+      </c>
+      <c r="G13" s="12">
         <v>6</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="12">
         <v>7</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B13+C13+D13+E13+F13)/3+G13/3+H13/3+I13,0))</f>
+      <c r="J13" s="13">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" s="13" t="n">
+      <c r="B14" s="13">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13">
+        <v>2</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13">
+        <v>2</v>
+      </c>
+      <c r="F14" s="13">
+        <v>2</v>
+      </c>
+      <c r="G14" s="13">
         <v>8</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="13">
         <v>7</v>
       </c>
       <c r="I14" s="13"/>
-      <c r="J14" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
+      <c r="J14" s="13">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="12">
         <v>2</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="12">
         <v>9</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="12">
         <v>4</v>
       </c>
       <c r="I15" s="12"/>
-      <c r="J15" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B15+C15+D15+E15+F15)/3+G15/3+H15/3+I15,0))</f>
+      <c r="J15" s="13">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="13" t="n">
+      <c r="B16" s="13">
+        <v>2</v>
+      </c>
+      <c r="C16" s="13">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2</v>
+      </c>
+      <c r="E16" s="13">
+        <v>2</v>
+      </c>
+      <c r="F16" s="13">
+        <v>2</v>
+      </c>
+      <c r="G16" s="13">
         <v>6</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="13">
         <v>7</v>
       </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="13" t="n">
-        <f aca="false">MIN(10, ROUNDUP((B16+C16+D16+E16+F16)/3+G16/3+H16/3+I16,0))</f>
+      <c r="J16" s="13">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
       <c r="K17" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="E26" s="14"/>
@@ -1854,14 +2155,14 @@
       <c r="BA26" s="14"/>
       <c r="BB26" s="14"/>
       <c r="BC26" s="14"/>
-      <c r="BD26" s="14" t="n">
+      <c r="BD26" s="14">
         <v>18</v>
       </c>
-      <c r="BE26" s="14" t="n">
+      <c r="BE26" s="14">
         <v>11</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="E27" s="14"/>
@@ -1915,14 +2216,14 @@
       <c r="BA27" s="14"/>
       <c r="BB27" s="14"/>
       <c r="BC27" s="14"/>
-      <c r="BD27" s="14" t="n">
+      <c r="BD27" s="14">
         <v>11</v>
       </c>
-      <c r="BE27" s="14" t="n">
+      <c r="BE27" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="E28" s="14"/>
@@ -1976,14 +2277,14 @@
       <c r="BA28" s="14"/>
       <c r="BB28" s="14"/>
       <c r="BC28" s="14"/>
-      <c r="BD28" s="14" t="n">
+      <c r="BD28" s="14">
         <v>0</v>
       </c>
-      <c r="BE28" s="14" t="n">
+      <c r="BE28" s="14">
         <v>54</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="E29" s="14"/>
@@ -2037,14 +2338,14 @@
       <c r="BA29" s="14"/>
       <c r="BB29" s="14"/>
       <c r="BC29" s="14"/>
-      <c r="BD29" s="14" t="n">
+      <c r="BD29" s="14">
         <v>8</v>
       </c>
-      <c r="BE29" s="14" t="n">
+      <c r="BE29" s="14">
         <v>31</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="E30" s="14"/>
@@ -2098,14 +2399,14 @@
       <c r="BA30" s="14"/>
       <c r="BB30" s="14"/>
       <c r="BC30" s="14"/>
-      <c r="BD30" s="14" t="n">
+      <c r="BD30" s="14">
         <v>21</v>
       </c>
-      <c r="BE30" s="14" t="n">
+      <c r="BE30" s="14">
         <v>36</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="E31" s="14"/>
@@ -2159,14 +2460,14 @@
       <c r="BA31" s="14"/>
       <c r="BB31" s="14"/>
       <c r="BC31" s="14"/>
-      <c r="BD31" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE31" s="14" t="n">
+      <c r="BD31" s="14">
+        <v>2</v>
+      </c>
+      <c r="BE31" s="14">
         <v>17</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="E32" s="14"/>
@@ -2220,14 +2521,14 @@
       <c r="BA32" s="14"/>
       <c r="BB32" s="14"/>
       <c r="BC32" s="14"/>
-      <c r="BD32" s="14" t="n">
+      <c r="BD32" s="14">
         <v>0</v>
       </c>
-      <c r="BE32" s="14" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BE32" s="14">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="E33" s="14"/>
@@ -2281,14 +2582,14 @@
       <c r="BA33" s="14"/>
       <c r="BB33" s="14"/>
       <c r="BC33" s="14"/>
-      <c r="BD33" s="14" t="n">
+      <c r="BD33" s="14">
         <v>23</v>
       </c>
-      <c r="BE33" s="14" t="n">
+      <c r="BE33" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="E34" s="14"/>
@@ -2342,14 +2643,14 @@
       <c r="BA34" s="14"/>
       <c r="BB34" s="14"/>
       <c r="BC34" s="14"/>
-      <c r="BD34" s="14" t="n">
+      <c r="BD34" s="14">
         <v>18</v>
       </c>
-      <c r="BE34" s="14" t="n">
+      <c r="BE34" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="E35" s="14"/>
@@ -2403,14 +2704,14 @@
       <c r="BA35" s="14"/>
       <c r="BB35" s="14"/>
       <c r="BC35" s="14"/>
-      <c r="BD35" s="14" t="n">
+      <c r="BD35" s="14">
         <v>17</v>
       </c>
-      <c r="BE35" s="14" t="n">
+      <c r="BE35" s="14">
         <v>14</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="E36" s="14"/>
@@ -2464,14 +2765,14 @@
       <c r="BA36" s="14"/>
       <c r="BB36" s="14"/>
       <c r="BC36" s="14"/>
-      <c r="BD36" s="14" t="n">
+      <c r="BD36" s="14">
         <v>17</v>
       </c>
-      <c r="BE36" s="14" t="n">
+      <c r="BE36" s="14">
         <v>46</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="E37" s="14"/>
@@ -2525,33 +2826,28 @@
       <c r="BA37" s="14"/>
       <c r="BB37" s="14"/>
       <c r="BC37" s="14"/>
-      <c r="BD37" s="14" t="n">
+      <c r="BD37" s="14">
         <v>18</v>
       </c>
-      <c r="BE37" s="14" t="n">
+      <c r="BE37" s="14">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="10"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2563,7 +2859,7 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12" t="s">
         <v>56</v>
@@ -2577,206 +2873,297 @@
       <c r="E2" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="13">
         <v>9</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13" t="n">
+      <c r="C3" s="13">
+        <f>(H6+I6)/2</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="13">
         <v>9</v>
       </c>
-      <c r="E3" s="12" t="n">
-        <f aca="false">MIN(ROUND((B3+C3+D3) / 3,0), 10)</f>
+      <c r="E3" s="12">
+        <f>MIN(ROUND((B3+C3+D3) / 3,0), 10)</f>
         <v>6</v>
       </c>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G3" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="12">
         <v>5</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="12">
+        <f>(H7+I7)/2</f>
+        <v>0</v>
+      </c>
       <c r="D4" s="12"/>
-      <c r="E4" s="12" t="n">
-        <f aca="false">MIN(ROUND((B4+C4+D4) / 3,0), 10)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E4" s="12">
+        <f>MIN(ROUND((B4+C4+D4) / 3,0), 10)</f>
+        <v>2</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="16"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
+      <c r="C5" s="13">
+        <v>10</v>
+      </c>
       <c r="D5" s="13"/>
-      <c r="E5" s="12" t="n">
-        <f aca="false">MIN(ROUND((C5+D5) / 2,0), 10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E5" s="12">
+        <f>MIN(ROUND((C5+D5) / 2,0), 10)</f>
+        <v>5</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="18"/>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="12">
         <v>10</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12" t="n">
+      <c r="C6" s="12">
+        <f>(H6+I6)/2</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="12">
         <v>9</v>
       </c>
-      <c r="E6" s="12" t="n">
-        <f aca="false">MIN(ROUND((B6+C6+D6) / 3,0), 10)</f>
+      <c r="E6" s="12">
+        <f t="shared" ref="E6:E15" si="0">MIN(ROUND((B6+C6+D6) / 3,0), 10)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G6" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="12">
         <v>5</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="12">
+        <f>(H5+I5)/2</f>
+        <v>0</v>
+      </c>
       <c r="D7" s="12"/>
-      <c r="E7" s="12" t="n">
-        <f aca="false">MIN(ROUND((B7+C7+D7) / 3,0), 10)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="21"/>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="12">
         <v>10</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12" t="n">
+      <c r="C8" s="12">
+        <f>(H7+I7)/2</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="12">
         <v>7</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <f aca="false">MIN(ROUND((B8+C8+D8) / 3,0), 10)</f>
+      <c r="E8" s="12">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G8" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="13">
         <v>8</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13" t="n">
+      <c r="C9" s="13">
+        <f>(H5+I5)/2</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="13">
         <v>9</v>
       </c>
-      <c r="E9" s="12" t="n">
-        <f aca="false">MIN(ROUND((B9+C9+D9) / 3,0), 10)</f>
+      <c r="E9" s="12">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="12">
         <v>5</v>
       </c>
-      <c r="C10" s="12"/>
+      <c r="C10" s="12">
+        <f>(H7+I7)/2</f>
+        <v>0</v>
+      </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="12" t="n">
-        <f aca="false">MIN(ROUND((B10+C10+D10) / 3,0), 10)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="13">
         <v>8</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13" t="n">
+      <c r="C11" s="13">
+        <f>(H3+I3)/2</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="13">
         <v>9</v>
       </c>
-      <c r="E11" s="12" t="n">
-        <f aca="false">MIN(ROUND((B11+C11+D11) / 3,0), 10)</f>
+      <c r="E11" s="12">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="12">
         <v>5</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="12">
+        <f>(H8+I8)/2</f>
+        <v>0</v>
+      </c>
       <c r="D12" s="12"/>
-      <c r="E12" s="12" t="n">
-        <f aca="false">MIN(ROUND((B12+C12+D12) / 3,0), 10)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="13">
         <v>8</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13" t="n">
+      <c r="C13" s="13">
+        <f>(H8+I8)/2</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="13">
         <v>9</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <f aca="false">MIN(ROUND((B13+C13+D13) / 3,0), 10)</f>
+      <c r="E13" s="12">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="12">
         <v>0</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
-      <c r="E14" s="12" t="n">
-        <f aca="false">MIN(ROUND((B14+C14+D14) / 3,0), 10)</f>
+      <c r="E14" s="12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="13">
         <v>5</v>
       </c>
-      <c r="C15" s="13"/>
+      <c r="C15" s="13">
+        <f>(H4+I4)/2</f>
+        <v>0</v>
+      </c>
       <c r="D15" s="13"/>
-      <c r="E15" s="12" t="n">
-        <f aca="false">MIN(ROUND((B15+C15+D15) / 3,0), 10)</f>
+      <c r="E15" s="12">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <conditionalFormatting sqref="E3:E15">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="2"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="2"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tutoring\FAKT_INFORMATICS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902C6767-0F6C-4C78-BA0A-0AF906E1098F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA2321B-BA47-451E-A779-C471080B877C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,7 +273,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,12 +300,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -318,13 +312,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,8 +429,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2905,7 +2899,7 @@
         <v>63</v>
       </c>
       <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
+      <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
@@ -2926,8 +2920,8 @@
       <c r="G4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="16"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="20"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -2945,8 +2939,8 @@
       <c r="G5" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="21"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
@@ -2969,8 +2963,8 @@
       <c r="G6" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="19"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
@@ -2991,8 +2985,8 @@
       <c r="G7" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="18"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -3015,8 +3009,8 @@
       <c r="G8" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">

--- a/marks.xlsx
+++ b/marks.xlsx
@@ -1,33 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\tutoring\FAKT_INFORMATICS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA2321B-BA47-451E-A779-C471080B877C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="посещения" sheetId="1" r:id="rId1"/>
-    <sheet name="оценки" sheetId="2" r:id="rId2"/>
-    <sheet name="оценки 2 семестр" sheetId="3" r:id="rId3"/>
+    <sheet name="посещения" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="оценки" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="оценки 2 семестр" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -38,218 +24,221 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="69">
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
-  </si>
-  <si>
-    <t>Column4</t>
-  </si>
-  <si>
-    <t>Column5</t>
-  </si>
-  <si>
-    <t>Column6</t>
-  </si>
-  <si>
-    <t>Column7</t>
-  </si>
-  <si>
-    <t>Column8</t>
-  </si>
-  <si>
-    <t>Column9</t>
-  </si>
-  <si>
-    <t>Column10</t>
-  </si>
-  <si>
-    <t>Column11</t>
-  </si>
-  <si>
-    <t>Column12</t>
-  </si>
-  <si>
-    <t>Column13</t>
-  </si>
-  <si>
-    <t>Column14</t>
-  </si>
-  <si>
-    <t>Column15</t>
-  </si>
-  <si>
-    <t>Column16</t>
-  </si>
-  <si>
-    <t>2025-09-01</t>
-  </si>
-  <si>
-    <t>2025-09-08</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>2025-09-29</t>
-  </si>
-  <si>
-    <t>2025-10-06</t>
-  </si>
-  <si>
-    <t>2025-10-13</t>
-  </si>
-  <si>
-    <t>2025-10-20</t>
-  </si>
-  <si>
-    <t>2025-10-27</t>
-  </si>
-  <si>
-    <t>2025-11-03</t>
-  </si>
-  <si>
-    <t>2025-11-10</t>
-  </si>
-  <si>
-    <t>2025-11-17</t>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>Алеев</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Блинов</t>
-  </si>
-  <si>
-    <t>Кирсанов</t>
-  </si>
-  <si>
-    <t>Коломоец</t>
-  </si>
-  <si>
-    <t>Кукушкин</t>
-  </si>
-  <si>
-    <t>Моисеев</t>
-  </si>
-  <si>
-    <t>Осипов</t>
+    <t xml:space="preserve">Column1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Алеев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Блинов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кирсанов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коломоец</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кукушкин</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моисеев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Осипов</t>
   </si>
   <si>
     <t xml:space="preserve">Погосян </t>
   </si>
   <si>
-    <t>Подкорытов</t>
-  </si>
-  <si>
-    <t>Титова</t>
-  </si>
-  <si>
-    <t>Фролова</t>
-  </si>
-  <si>
-    <t>Хачоян</t>
-  </si>
-  <si>
-    <t>Цагадаев</t>
-  </si>
-  <si>
-    <t>Чернейко</t>
-  </si>
-  <si>
-    <t>лаба1</t>
-  </si>
-  <si>
-    <t>лаба2</t>
-  </si>
-  <si>
-    <t>лаба3</t>
-  </si>
-  <si>
-    <t>лаба4</t>
-  </si>
-  <si>
-    <t>лаба5</t>
-  </si>
-  <si>
-    <t>КР1</t>
-  </si>
-  <si>
-    <t>КР2</t>
-  </si>
-  <si>
-    <t>доп баллы</t>
-  </si>
-  <si>
-    <t>итог</t>
-  </si>
-  <si>
-    <t>Кр / хакатон</t>
-  </si>
-  <si>
-    <t>проект</t>
-  </si>
-  <si>
-    <t>теор. Зачёт</t>
-  </si>
-  <si>
-    <t>Итог</t>
-  </si>
-  <si>
-    <t>review</t>
-  </si>
-  <si>
-    <t>fixes</t>
-  </si>
-  <si>
-    <t>team</t>
-  </si>
-  <si>
-    <t>Lunar Base Simulator</t>
-  </si>
-  <si>
-    <t>Strategy Game</t>
-  </si>
-  <si>
-    <t>Bank</t>
-  </si>
-  <si>
-    <t>Морской бой</t>
-  </si>
-  <si>
-    <t>бот для бронирования</t>
-  </si>
-  <si>
-    <t>лифт</t>
+    <t xml:space="preserve">Подкорытов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Титова</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фролова</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Хачоян</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цагадаев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чернейко</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лаба5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КР1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КР2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">доп баллы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">итог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кр / хакатон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">проект</t>
+  </si>
+  <si>
+    <t xml:space="preserve">теор. Зачёт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Итог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunar Base Simulator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Морской бой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">бот для бронирования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лифт</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -258,7 +247,22 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -273,7 +277,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,49 +293,43 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0D9"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFDEEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFDEEBF7"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFDBDBDB"/>
+        <bgColor rgb="FFDEEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFDBDBDB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="7">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFA9D18E"/>
       </left>
@@ -344,7 +342,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top style="thin">
@@ -355,7 +353,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FFA9D18E"/>
@@ -368,7 +366,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFA9D18E"/>
       </left>
@@ -379,7 +377,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top style="thin">
@@ -388,56 +386,138 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+  <cellXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Пояснение" xfId="1" builtinId="53" customBuiltin="1"/>
+  <cellStyles count="7">
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -458,12 +538,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFDEEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDBDBDB"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -479,7 +559,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -496,331 +576,23 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
-  <a:themeElements>
-    <a:clrScheme name="Стандартная">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4472C4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Стандартная">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1025" width="8.7109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,7 +642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="5" t="s">
         <v>16</v>
@@ -918,7 +690,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
@@ -968,7 +740,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>34</v>
       </c>
@@ -1018,7 +790,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1068,7 +840,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>36</v>
       </c>
@@ -1078,7 +850,7 @@
       <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -1118,7 +890,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -1168,7 +940,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
@@ -1218,7 +990,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
@@ -1268,7 +1040,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>40</v>
       </c>
@@ -1287,7 +1059,7 @@
       <c r="F10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -1318,7 +1090,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -1368,7 +1140,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
         <v>42</v>
       </c>
@@ -1418,7 +1190,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1434,10 +1206,10 @@
       <c r="E13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="s">
@@ -1468,7 +1240,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
@@ -1518,7 +1290,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>45</v>
       </c>
@@ -1568,7 +1340,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -1619,23 +1391,31 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:BE37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="1025" width="8.7109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="10" style="0" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1647,7 +1427,7 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12"/>
       <c r="B2" s="12" t="s">
         <v>47</v>
@@ -1677,253 +1457,253 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="13">
-        <v>2</v>
-      </c>
-      <c r="C3" s="13">
-        <v>2</v>
-      </c>
-      <c r="D3" s="13">
-        <v>2</v>
-      </c>
-      <c r="E3" s="13">
-        <v>2</v>
-      </c>
-      <c r="F3" s="13">
-        <v>2</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="B3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="13" t="n">
         <v>8</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="13">
-        <f t="shared" ref="J3:J16" si="0">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
+      <c r="J3" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B3+C3+D3+E3+F3)/3+G3/3+H3/3+I3,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="12">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12">
-        <v>2</v>
-      </c>
-      <c r="D4" s="12">
-        <v>2</v>
-      </c>
-      <c r="E4" s="12">
-        <v>2</v>
-      </c>
-      <c r="F4" s="12">
-        <v>2</v>
-      </c>
-      <c r="G4" s="12">
+      <c r="B4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I4" s="12"/>
-      <c r="J4" s="13">
-        <f t="shared" si="0"/>
+      <c r="J4" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B4+C4+D4+E4+F4)/3+G4/3+H4/3+I4,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="13">
-        <v>2</v>
-      </c>
-      <c r="C5" s="13">
-        <v>2</v>
-      </c>
-      <c r="D5" s="13">
-        <v>2</v>
-      </c>
-      <c r="E5" s="13">
-        <v>2</v>
-      </c>
-      <c r="F5" s="13">
-        <v>2</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="B5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="13" t="n">
         <v>7</v>
       </c>
       <c r="I5" s="13"/>
-      <c r="J5" s="13">
-        <f t="shared" si="0"/>
+      <c r="J5" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B5+C5+D5+E5+F5)/3+G5/3+H5/3+I5,0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="12">
-        <v>2</v>
-      </c>
-      <c r="C6" s="12">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12">
-        <v>2</v>
-      </c>
-      <c r="E6" s="12">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12">
-        <v>2</v>
-      </c>
-      <c r="G6" s="12">
+      <c r="B6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I6" s="12"/>
-      <c r="J6" s="13">
-        <f t="shared" si="0"/>
+      <c r="J6" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B6+C6+D6+E6+F6)/3+G6/3+H6/3+I6,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="12">
-        <v>2</v>
-      </c>
-      <c r="C7" s="12">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12">
-        <v>2</v>
-      </c>
-      <c r="E7" s="12">
-        <v>2</v>
-      </c>
-      <c r="F7" s="12">
-        <v>2</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="B7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I7" s="12"/>
-      <c r="J7" s="13">
-        <f t="shared" si="0"/>
+      <c r="J7" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B7+C7+D7+E7+F7)/3+G7/3+H7/3+I7,0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="12">
-        <v>2</v>
-      </c>
-      <c r="E8" s="12">
-        <v>2</v>
-      </c>
-      <c r="F8" s="12">
-        <v>2</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="D8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I8" s="12"/>
-      <c r="J8" s="13">
-        <f t="shared" si="0"/>
+      <c r="J8" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B8+C8+D8+E8+F8)/3+G8/3+H8/3+I8,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="13">
-        <v>2</v>
-      </c>
-      <c r="C9" s="13">
-        <v>2</v>
-      </c>
-      <c r="D9" s="13">
-        <v>2</v>
-      </c>
-      <c r="E9" s="13">
-        <v>2</v>
-      </c>
-      <c r="F9" s="13">
-        <v>2</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="B9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="13" t="n">
         <v>10</v>
       </c>
       <c r="I9" s="13"/>
-      <c r="J9" s="13">
-        <f t="shared" si="0"/>
+      <c r="J9" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B9+C9+D9+E9+F9)/3+G9/3+H9/3+I9,0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12">
-        <v>2</v>
-      </c>
-      <c r="C10" s="12">
-        <v>2</v>
-      </c>
-      <c r="D10" s="12">
-        <v>2</v>
-      </c>
-      <c r="E10" s="12">
-        <v>2</v>
-      </c>
-      <c r="F10" s="12">
-        <v>2</v>
-      </c>
-      <c r="G10" s="12">
+      <c r="B10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="13">
-        <f t="shared" si="0"/>
+      <c r="J10" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B10+C10+D10+E10+F10)/3+G10/3+H10/3+I10,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -1932,170 +1712,170 @@
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="13">
+      <c r="G11" s="13" t="n">
         <v>10</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
-      <c r="J11" s="13">
-        <f t="shared" si="0"/>
+      <c r="J11" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B11+C11+D11+E11+F11)/3+G11/3+H11/3+I11,0))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="13">
-        <v>2</v>
-      </c>
-      <c r="C12" s="13">
-        <v>2</v>
-      </c>
-      <c r="D12" s="13">
-        <v>2</v>
-      </c>
-      <c r="E12" s="13">
-        <v>2</v>
-      </c>
-      <c r="F12" s="13">
-        <v>2</v>
-      </c>
-      <c r="G12" s="13">
+      <c r="B12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="13" t="n">
         <v>6</v>
       </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="13">
-        <f t="shared" si="0"/>
+      <c r="J12" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B12+C12+D12+E12+F12)/3+G12/3+H12/3+I12,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
-      <c r="D13" s="12">
-        <v>2</v>
-      </c>
-      <c r="E13" s="12">
-        <v>2</v>
-      </c>
-      <c r="F13" s="12">
-        <v>2</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="D13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="13">
-        <f t="shared" si="0"/>
+      <c r="J13" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B13+C13+D13+E13+F13)/3+G13/3+H13/3+I13,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="13">
-        <v>2</v>
-      </c>
-      <c r="C14" s="13">
-        <v>2</v>
-      </c>
-      <c r="D14" s="13">
-        <v>2</v>
-      </c>
-      <c r="E14" s="13">
-        <v>2</v>
-      </c>
-      <c r="F14" s="13">
-        <v>2</v>
-      </c>
-      <c r="G14" s="13">
+      <c r="B14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="13" t="n">
         <v>7</v>
       </c>
       <c r="I14" s="13"/>
-      <c r="J14" s="13">
-        <f t="shared" si="0"/>
+      <c r="J14" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B14+C14+D14+E14+F14)/3+G14/3+H14/3+I14,0))</f>
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="12">
+      <c r="C15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="12">
+      <c r="G15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I15" s="12"/>
-      <c r="J15" s="13">
-        <f t="shared" si="0"/>
+      <c r="J15" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B15+C15+D15+E15+F15)/3+G15/3+H15/3+I15,0))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="13">
-        <v>2</v>
-      </c>
-      <c r="C16" s="13">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13">
-        <v>2</v>
-      </c>
-      <c r="E16" s="13">
-        <v>2</v>
-      </c>
-      <c r="F16" s="13">
-        <v>2</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="B16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="13" t="n">
         <v>7</v>
       </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="13">
-        <f t="shared" si="0"/>
+      <c r="J16" s="13" t="n">
+        <f aca="false">MIN(10, ROUNDUP((B16+C16+D16+E16+F16)/3+G16/3+H16/3+I16,0))</f>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K17" s="8"/>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="9"/>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="E26" s="14"/>
@@ -2149,14 +1929,14 @@
       <c r="BA26" s="14"/>
       <c r="BB26" s="14"/>
       <c r="BC26" s="14"/>
-      <c r="BD26" s="14">
+      <c r="BD26" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE26" s="14">
+      <c r="BE26" s="14" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="E27" s="14"/>
@@ -2210,14 +1990,14 @@
       <c r="BA27" s="14"/>
       <c r="BB27" s="14"/>
       <c r="BC27" s="14"/>
-      <c r="BD27" s="14">
+      <c r="BD27" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="BE27" s="14">
+      <c r="BE27" s="14" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="E28" s="14"/>
@@ -2271,14 +2051,14 @@
       <c r="BA28" s="14"/>
       <c r="BB28" s="14"/>
       <c r="BC28" s="14"/>
-      <c r="BD28" s="14">
+      <c r="BD28" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BE28" s="14">
+      <c r="BE28" s="14" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="E29" s="14"/>
@@ -2332,14 +2112,14 @@
       <c r="BA29" s="14"/>
       <c r="BB29" s="14"/>
       <c r="BC29" s="14"/>
-      <c r="BD29" s="14">
+      <c r="BD29" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="BE29" s="14">
+      <c r="BE29" s="14" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="E30" s="14"/>
@@ -2393,14 +2173,14 @@
       <c r="BA30" s="14"/>
       <c r="BB30" s="14"/>
       <c r="BC30" s="14"/>
-      <c r="BD30" s="14">
+      <c r="BD30" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="BE30" s="14">
+      <c r="BE30" s="14" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="E31" s="14"/>
@@ -2454,14 +2234,14 @@
       <c r="BA31" s="14"/>
       <c r="BB31" s="14"/>
       <c r="BC31" s="14"/>
-      <c r="BD31" s="14">
-        <v>2</v>
-      </c>
-      <c r="BE31" s="14">
+      <c r="BD31" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE31" s="14" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="E32" s="14"/>
@@ -2515,14 +2295,14 @@
       <c r="BA32" s="14"/>
       <c r="BB32" s="14"/>
       <c r="BC32" s="14"/>
-      <c r="BD32" s="14">
+      <c r="BD32" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BE32" s="14">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="BE32" s="14" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="E33" s="14"/>
@@ -2576,14 +2356,14 @@
       <c r="BA33" s="14"/>
       <c r="BB33" s="14"/>
       <c r="BC33" s="14"/>
-      <c r="BD33" s="14">
+      <c r="BD33" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="BE33" s="14">
+      <c r="BE33" s="14" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="E34" s="14"/>
@@ -2637,14 +2417,14 @@
       <c r="BA34" s="14"/>
       <c r="BB34" s="14"/>
       <c r="BC34" s="14"/>
-      <c r="BD34" s="14">
+      <c r="BD34" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE34" s="14">
+      <c r="BE34" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14"/>
       <c r="B35" s="14"/>
       <c r="E35" s="14"/>
@@ -2698,14 +2478,14 @@
       <c r="BA35" s="14"/>
       <c r="BB35" s="14"/>
       <c r="BC35" s="14"/>
-      <c r="BD35" s="14">
+      <c r="BD35" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="BE35" s="14">
+      <c r="BE35" s="14" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14"/>
       <c r="B36" s="14"/>
       <c r="E36" s="14"/>
@@ -2759,14 +2539,14 @@
       <c r="BA36" s="14"/>
       <c r="BB36" s="14"/>
       <c r="BC36" s="14"/>
-      <c r="BD36" s="14">
+      <c r="BD36" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="BE36" s="14">
+      <c r="BE36" s="14" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14"/>
       <c r="B37" s="14"/>
       <c r="E37" s="14"/>
@@ -2820,28 +2600,40 @@
       <c r="BA37" s="14"/>
       <c r="BB37" s="14"/>
       <c r="BC37" s="14"/>
-      <c r="BD37" s="14">
+      <c r="BD37" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="BE37" s="14">
+      <c r="BE37" s="14" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="8.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="0" width="8.6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10"/>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2853,7 +2645,7 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12"/>
       <c r="B2" s="12" t="s">
         <v>56</v>
@@ -2868,283 +2660,313 @@
         <v>59</v>
       </c>
       <c r="G2" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="13">
-        <f>(H6+I6)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="13">
+      <c r="C3" s="13" t="n">
+        <f aca="false">(H6+I6)/2</f>
+        <v>8</v>
+      </c>
+      <c r="D3" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="E3" s="12">
-        <f>MIN(ROUND((B3+C3+D3) / 3,0), 10)</f>
+      <c r="E3" s="12" t="n">
+        <f aca="false">MIN(ROUND((B3+C3+D3) / 3,0), 10)</f>
+        <v>9</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="21"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I3" s="16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="12">
-        <v>5</v>
-      </c>
-      <c r="C4" s="12">
-        <f>(H7+I7)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12">
-        <f>MIN(ROUND((B4+C4+D4) / 3,0), 10)</f>
-        <v>2</v>
-      </c>
-      <c r="G4" s="15" t="s">
+      <c r="B4" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <f aca="false">(H7+8)/2</f>
+        <v>7</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <f aca="false">MIN(ROUND((B4+C4+D4) / 3,0), 10)</f>
+        <v>7</v>
+      </c>
+      <c r="G4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="20"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H4" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="13"/>
-      <c r="C5" s="13">
+      <c r="C5" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="12">
-        <f>MIN(ROUND((C5+D5) / 2,0), 10)</f>
-        <v>5</v>
-      </c>
-      <c r="G5" s="15" t="s">
+      <c r="D5" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <f aca="false">MIN(ROUND((C5+D5) / 2,0), 10)</f>
+        <v>9</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="12">
-        <f>(H6+I6)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C6" s="12" t="n">
+        <f aca="false">(H6+I6)/2</f>
+        <v>8</v>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="12">
-        <f t="shared" ref="E6:E15" si="0">MIN(ROUND((B6+C6+D6) / 3,0), 10)</f>
-        <v>6</v>
-      </c>
-      <c r="G6" s="15" t="s">
+      <c r="E6" s="12" t="n">
+        <f aca="false">MIN(ROUND((B6+C6+D6) / 3,0), 10)</f>
+        <v>9</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="12">
-        <f>(H5+I5)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="G7" s="15" t="s">
+      <c r="C7" s="12" t="n">
+        <f aca="false">(H5+I5)/2</f>
+        <v>8</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <f aca="false">MIN(ROUND((B7+C7+D7) / 3,0), 10)</f>
+        <v>7</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="19"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="12">
-        <f>(H7+I7)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="12" t="n">
+        <f aca="false">(H7+I7)/2</f>
+        <v>6.5</v>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="12">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="G8" s="15" t="s">
+      <c r="E8" s="12" t="n">
+        <f aca="false">MIN(ROUND((B8+C8+D8) / 3,0), 10)</f>
+        <v>8</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H8" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <f aca="false">(H5+I5)/2</f>
         <v>8</v>
       </c>
-      <c r="C9" s="13">
-        <f>(H5+I5)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="13">
+      <c r="D9" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="12">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E9" s="12" t="n">
+        <f aca="false">MIN(ROUND((B9+C9+D9) / 3,0), 10)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12">
-        <v>5</v>
-      </c>
-      <c r="C10" s="12">
-        <f>(H7+I7)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <f aca="false">(H7+I7)/2</f>
+        <v>6.5</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <f aca="false">MIN(ROUND((B10+C10+D10) / 3,0), 10)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="13">
-        <f>(H3+I3)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="C11" s="13" t="n">
+        <f aca="false">(H3+I3)/2</f>
+        <v>6.5</v>
+      </c>
+      <c r="D11" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="12">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E11" s="12" t="n">
+        <f aca="false">MIN(ROUND((B11+C11+D11) / 3,0), 10)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="12">
-        <f>(H8+I8)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C12" s="12" t="n">
+        <f aca="false">(H8+I8)/2</f>
+        <v>8</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <f aca="false">MIN(ROUND((B12+C12+D12) / 3,0), 10)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="13">
-        <f>(H8+I8)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="C13" s="13" t="n">
+        <f aca="false">(H8+I8)/2</f>
+        <v>8</v>
+      </c>
+      <c r="D13" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="12">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E13" s="12" t="n">
+        <f aca="false">MIN(ROUND((B13+C13+D13) / 3,0), 10)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
-      <c r="E14" s="12">
-        <f t="shared" si="0"/>
+      <c r="E14" s="12" t="n">
+        <f aca="false">MIN(ROUND((B14+C14+D14) / 3,0), 10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="13">
-        <f>(H4+I4)/2</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="12">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
+      <c r="C15" s="13" t="n">
+        <f aca="false">(H4+I4)/2</f>
+        <v>8</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <f aca="false">MIN(ROUND((B15+C15+D15) / 3,0), 10)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <conditionalFormatting sqref="E3:E15">
     <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="2"/>
-        <cfvo type="num" val="10"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="2"/>
         <cfvo type="num" val="5"/>
@@ -3154,10 +2976,19 @@
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="2"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
